--- a/Clase_00/Base_1_TimeSeries.xlsx
+++ b/Clase_00/Base_1_TimeSeries.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin/Documents/Personal/Cursos_UNAM/SERIES_2025-I/Series-Tiempo-2024/Clase_00/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin/Documents/Personal/Cursos_Tec/Econometría II/Econometria-II-2025-Tec/Clase_00/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C4B535-B03E-E74F-8D07-43E63430F918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D865FF8-435F-804A-A131-F7C81ACA9012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32100" yWindow="2780" windowWidth="27640" windowHeight="16540" xr2:uid="{0D46E9FE-A0A6-634E-B88F-BB6E7EC27F03}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="288">
   <si>
     <t>Periodo</t>
   </si>
@@ -813,49 +813,82 @@
     <t>2023/05</t>
   </si>
   <si>
+    <t>2023/06</t>
+  </si>
+  <si>
+    <t>2023/07</t>
+  </si>
+  <si>
+    <t>2023/08</t>
+  </si>
+  <si>
+    <t>2023/09</t>
+  </si>
+  <si>
+    <t>2023/10</t>
+  </si>
+  <si>
+    <t>2023/11</t>
+  </si>
+  <si>
+    <t>2023/12</t>
+  </si>
+  <si>
+    <t>2024/01</t>
+  </si>
+  <si>
+    <t>2024/02</t>
+  </si>
+  <si>
+    <t>2024/03</t>
+  </si>
+  <si>
+    <t>2024/04</t>
+  </si>
+  <si>
+    <t>2024/05</t>
+  </si>
+  <si>
+    <t>2024/06</t>
+  </si>
+  <si>
+    <t>2024/07</t>
+  </si>
+  <si>
+    <t>2024/08</t>
+  </si>
+  <si>
+    <t>2024/09</t>
+  </si>
+  <si>
+    <t>2024/10</t>
+  </si>
+  <si>
+    <t>2024/11</t>
+  </si>
+  <si>
+    <t>2024/12</t>
+  </si>
+  <si>
+    <t>2025/01</t>
+  </si>
+  <si>
+    <t>2025/02</t>
+  </si>
+  <si>
+    <t>2025/03</t>
+  </si>
+  <si>
+    <t>2025/04</t>
+  </si>
+  <si>
+    <t>2025/05</t>
+  </si>
+  <si>
     <t>IGAE_2018</t>
   </si>
   <si>
     <t>IGAE_PRIM_2018</t>
-  </si>
-  <si>
-    <t>2023/06</t>
-  </si>
-  <si>
-    <t>2023/07</t>
-  </si>
-  <si>
-    <t>2023/08</t>
-  </si>
-  <si>
-    <t>2023/09</t>
-  </si>
-  <si>
-    <t>2023/10</t>
-  </si>
-  <si>
-    <t>2023/11</t>
-  </si>
-  <si>
-    <t>2023/12</t>
-  </si>
-  <si>
-    <t>2024/01</t>
-  </si>
-  <si>
-    <t>2024/02</t>
-  </si>
-  <si>
-    <t>2024/03</t>
-  </si>
-  <si>
-    <t>2024/04</t>
-  </si>
-  <si>
-    <t>2024/05</t>
-  </si>
-  <si>
-    <t>2024/06</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1246,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033E69B6-2D16-514E-A726-941639C52B74}">
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1221,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C1" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="D1" t="s">
         <v>200</v>
@@ -1244,10 +1277,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>71.112734477095998</v>
+        <v>70.583749647092006</v>
       </c>
       <c r="C2">
-        <v>76.060817880786004</v>
+        <v>76.060817880786999</v>
       </c>
       <c r="D2">
         <v>36.927558573412</v>
@@ -1259,7 +1292,7 @@
         <v>6927.87</v>
       </c>
       <c r="G2">
-        <v>9.1463000000000001</v>
+        <v>9.1616</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1267,10 +1300,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>68.966554728160006</v>
+        <v>69.194394152379004</v>
       </c>
       <c r="C3">
-        <v>66.179852479339004</v>
+        <v>66.179852479339999</v>
       </c>
       <c r="D3">
         <v>37.597942107675998</v>
@@ -1282,7 +1315,7 @@
         <v>6734.44</v>
       </c>
       <c r="G3">
-        <v>9.1303000000000001</v>
+        <v>9.0998000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -1290,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>70.535946879972002</v>
+        <v>72.592518531376001</v>
       </c>
       <c r="C4">
         <v>64.961236820533003</v>
@@ -1305,7 +1338,7 @@
         <v>7361.86</v>
       </c>
       <c r="G4">
-        <v>9.016</v>
+        <v>9.0707000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -1313,7 +1346,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>74.858038086774997</v>
+        <v>72.983456730922995</v>
       </c>
       <c r="C5">
         <v>65.887143744194006</v>
@@ -1328,7 +1361,7 @@
         <v>7480.74</v>
       </c>
       <c r="G5">
-        <v>9.3719999999999999</v>
+        <v>9.1629000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -1336,10 +1369,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>74.712776096211996</v>
+        <v>74.208871115049007</v>
       </c>
       <c r="C6">
-        <v>75.950278687817999</v>
+        <v>75.950278687818994</v>
       </c>
       <c r="D6">
         <v>41.630049645459998</v>
@@ -1351,7 +1384,7 @@
         <v>7031.64</v>
       </c>
       <c r="G6">
-        <v>9.6562000000000001</v>
+        <v>9.5191999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -1359,10 +1392,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>72.863379843811003</v>
+        <v>73.701724746395001</v>
       </c>
       <c r="C7">
-        <v>79.721720678522999</v>
+        <v>79.721720678523994</v>
       </c>
       <c r="D7">
         <v>41.547499507034999</v>
@@ -1374,7 +1407,7 @@
         <v>6460.95</v>
       </c>
       <c r="G7">
-        <v>9.9567999999999994</v>
+        <v>9.7652000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -1382,7 +1415,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>73.619611596159004</v>
+        <v>73.128225042704997</v>
       </c>
       <c r="C8">
         <v>72.112697529377002</v>
@@ -1397,7 +1430,7 @@
         <v>6021.84</v>
       </c>
       <c r="G8">
-        <v>9.7860999999999994</v>
+        <v>9.7807999999999993</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -1405,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>73.891727114017002</v>
+        <v>73.797243601538995</v>
       </c>
       <c r="C9">
         <v>64.513030242818004</v>
@@ -1420,7 +1453,7 @@
         <v>6216.43</v>
       </c>
       <c r="G9">
-        <v>9.9108999999999998</v>
+        <v>9.8396000000000008</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -1428,7 +1461,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>73.956599931566004</v>
+        <v>74.506493376551006</v>
       </c>
       <c r="C10">
         <v>59.053447527995999</v>
@@ -1443,7 +1476,7 @@
         <v>5728.46</v>
       </c>
       <c r="G10">
-        <v>10.229900000000001</v>
+        <v>10.071400000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -1451,10 +1484,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>74.951192521606004</v>
+        <v>74.393185771928998</v>
       </c>
       <c r="C11">
-        <v>66.292061836084002</v>
+        <v>66.292061836082993</v>
       </c>
       <c r="D11">
         <v>41.005364954704</v>
@@ -1466,7 +1499,7 @@
         <v>5967.73</v>
       </c>
       <c r="G11">
-        <v>10.155200000000001</v>
+        <v>10.095000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -1474,10 +1507,10 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>73.359600857648005</v>
+        <v>73.364972535443002</v>
       </c>
       <c r="C12">
-        <v>82.358956560642994</v>
+        <v>82.358956560642</v>
       </c>
       <c r="D12">
         <v>42.111526092018003</v>
@@ -1489,7 +1522,7 @@
         <v>6156.83</v>
       </c>
       <c r="G12">
-        <v>10.1465</v>
+        <v>10.1975</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -1497,10 +1530,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>73.873536808291007</v>
+        <v>74.118978295919007</v>
       </c>
       <c r="C13">
-        <v>84.432239801182007</v>
+        <v>84.432239801180003</v>
       </c>
       <c r="D13">
         <v>42.914961613891002</v>
@@ -1512,7 +1545,7 @@
         <v>6127.09</v>
       </c>
       <c r="G13">
-        <v>10.439299999999999</v>
+        <v>10.2249</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -1520,10 +1553,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>72.570800210946999</v>
+        <v>72.081324343690994</v>
       </c>
       <c r="C14">
-        <v>78.772727303881993</v>
+        <v>78.772727303878995</v>
       </c>
       <c r="D14">
         <v>40.884979005161</v>
@@ -1535,7 +1568,7 @@
         <v>5954.35</v>
       </c>
       <c r="G14">
-        <v>10.9069</v>
+        <v>10.6203</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -1543,10 +1576,10 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>70.941246035738004</v>
+        <v>71.174902715268004</v>
       </c>
       <c r="C15">
-        <v>67.587174379093995</v>
+        <v>67.587174379092005</v>
       </c>
       <c r="D15">
         <v>39.148309064803001</v>
@@ -1558,7 +1591,7 @@
         <v>5927.06</v>
       </c>
       <c r="G15">
-        <v>11.032400000000001</v>
+        <v>10.937200000000001</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -1566,10 +1599,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>73.522296486311006</v>
+        <v>73.679288962806993</v>
       </c>
       <c r="C16">
-        <v>66.484655829469006</v>
+        <v>66.484655829467002</v>
       </c>
       <c r="D16">
         <v>37.882144218617</v>
@@ -1581,7 +1614,7 @@
         <v>5914.03</v>
       </c>
       <c r="G16">
-        <v>10.7889</v>
+        <v>10.9124</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1589,10 +1622,10 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>73.556142425819004</v>
+        <v>73.747926225388994</v>
       </c>
       <c r="C17">
-        <v>67.365466898530002</v>
+        <v>67.365466898527998</v>
       </c>
       <c r="D17">
         <v>40.005031711850002</v>
@@ -1604,7 +1637,7 @@
         <v>6509.88</v>
       </c>
       <c r="G17">
-        <v>10.3</v>
+        <v>10.591699999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -1612,10 +1645,10 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>74.759866432207005</v>
+        <v>74.664130510082998</v>
       </c>
       <c r="C18">
-        <v>75.355370536867994</v>
+        <v>75.355370536864996</v>
       </c>
       <c r="D18">
         <v>40.957565736684003</v>
@@ -1627,7 +1660,7 @@
         <v>6699.18</v>
       </c>
       <c r="G18">
-        <v>10.3377</v>
+        <v>10.251200000000001</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -1635,10 +1668,10 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>74.308724446572995</v>
+        <v>74.861108702598997</v>
       </c>
       <c r="C19">
-        <v>87.499106777750001</v>
+        <v>87.499106777747002</v>
       </c>
       <c r="D19">
         <v>41.352470524521003</v>
@@ -1650,7 +1683,7 @@
         <v>7054.99</v>
       </c>
       <c r="G19">
-        <v>10.436999999999999</v>
+        <v>10.5047</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -1658,10 +1691,10 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>74.207327714342</v>
+        <v>73.654722906665995</v>
       </c>
       <c r="C20">
-        <v>77.239821583216994</v>
+        <v>77.239821583215999</v>
       </c>
       <c r="D20">
         <v>41.377350711883999</v>
@@ -1673,7 +1706,7 @@
         <v>7355.07</v>
       </c>
       <c r="G20">
-        <v>10.5243</v>
+        <v>10.450200000000001</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -1681,7 +1714,7 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>72.618939738110996</v>
+        <v>73.206182846738997</v>
       </c>
       <c r="C21">
         <v>64.196182513742002</v>
@@ -1696,7 +1729,7 @@
         <v>7591.42</v>
       </c>
       <c r="G21">
-        <v>11.047499999999999</v>
+        <v>10.7811</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1704,10 +1737,10 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>74.302477579568006</v>
+        <v>73.955461492688002</v>
       </c>
       <c r="C22">
-        <v>61.471991990291997</v>
+        <v>61.471991990292999</v>
       </c>
       <c r="D22">
         <v>40.095952771034</v>
@@ -1719,7 +1752,7 @@
         <v>7822.48</v>
       </c>
       <c r="G22">
-        <v>11.013299999999999</v>
+        <v>10.9269</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1727,10 +1760,10 @@
         <v>24</v>
       </c>
       <c r="B23">
-        <v>74.775799788387005</v>
+        <v>74.271446020089002</v>
       </c>
       <c r="C23">
-        <v>61.252990526860003</v>
+        <v>61.252990526862</v>
       </c>
       <c r="D23">
         <v>39.822303594204001</v>
@@ -1742,7 +1775,7 @@
         <v>8064.83</v>
       </c>
       <c r="G23">
-        <v>11.0525</v>
+        <v>11.174799999999999</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -1750,10 +1783,10 @@
         <v>25</v>
       </c>
       <c r="B24">
-        <v>72.965023310118994</v>
+        <v>73.804898866650007</v>
       </c>
       <c r="C24">
-        <v>88.913288849720004</v>
+        <v>88.913288849726001</v>
       </c>
       <c r="D24">
         <v>39.155114573469</v>
@@ -1765,7 +1798,7 @@
         <v>8554.48</v>
       </c>
       <c r="G24">
-        <v>11.3985</v>
+        <v>11.145</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1773,10 +1806,10 @@
         <v>26</v>
       </c>
       <c r="B25">
-        <v>76.157523369147995</v>
+        <v>75.649271431707007</v>
       </c>
       <c r="C25">
-        <v>90.713361612797996</v>
+        <v>90.713361612805997</v>
       </c>
       <c r="D25">
         <v>39.600450099566999</v>
@@ -1788,7 +1821,7 @@
         <v>8795.2800000000007</v>
       </c>
       <c r="G25">
-        <v>11.2372</v>
+        <v>11.2486</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1796,10 +1829,10 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>73.610181304194995</v>
+        <v>73.515605228026004</v>
       </c>
       <c r="C26">
-        <v>87.815447561734999</v>
+        <v>87.815447561747007</v>
       </c>
       <c r="D26">
         <v>39.629821475025999</v>
@@ -1811,7 +1844,7 @@
         <v>9428.77</v>
       </c>
       <c r="G26">
-        <v>11.0214</v>
+        <v>10.915100000000001</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -1819,10 +1852,10 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>72.557269622152006</v>
+        <v>72.420021735221994</v>
       </c>
       <c r="C27">
-        <v>75.149784061695996</v>
+        <v>75.149784061706001</v>
       </c>
       <c r="D27">
         <v>39.437491418458997</v>
@@ -1834,7 +1867,7 @@
         <v>9991.7999999999993</v>
       </c>
       <c r="G27">
-        <v>11.060600000000001</v>
+        <v>11.014200000000001</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1842,10 +1875,10 @@
         <v>29</v>
       </c>
       <c r="B28">
-        <v>77.760942083765002</v>
+        <v>76.570554247925998</v>
       </c>
       <c r="C28">
-        <v>68.220501814005999</v>
+        <v>68.220501814014995</v>
       </c>
       <c r="D28">
         <v>39.626755192928997</v>
@@ -1857,7 +1890,7 @@
         <v>10517.5</v>
       </c>
       <c r="G28">
-        <v>11.174799999999999</v>
+        <v>11.009399999999999</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1865,10 +1898,10 @@
         <v>30</v>
       </c>
       <c r="B29">
-        <v>76.01497934919</v>
+        <v>76.318309767892998</v>
       </c>
       <c r="C29">
-        <v>70.216757052771996</v>
+        <v>70.216757052781006</v>
       </c>
       <c r="D29">
         <v>39.752330848820002</v>
@@ -1880,7 +1913,7 @@
         <v>9948.1299999999992</v>
       </c>
       <c r="G29">
-        <v>11.4093</v>
+        <v>11.2751</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1888,10 +1921,10 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>76.995096424517001</v>
+        <v>77.835891213815003</v>
       </c>
       <c r="C30">
-        <v>77.802659830891997</v>
+        <v>77.802659830902002</v>
       </c>
       <c r="D30">
         <v>41.079092185707999</v>
@@ -1903,7 +1936,7 @@
         <v>10036.290000000001</v>
       </c>
       <c r="G30">
-        <v>11.4147</v>
+        <v>11.5124</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1911,10 +1944,10 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>77.969018515094007</v>
+        <v>77.493344897333998</v>
       </c>
       <c r="C31">
-        <v>84.827823379744999</v>
+        <v>84.827823379752999</v>
       </c>
       <c r="D31">
         <v>41.079287995192999</v>
@@ -1926,7 +1959,7 @@
         <v>10281.82</v>
       </c>
       <c r="G31">
-        <v>11.5258</v>
+        <v>11.3894</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1934,10 +1967,10 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>75.763272207821998</v>
+        <v>75.665844299564</v>
       </c>
       <c r="C32">
-        <v>74.945761404245005</v>
+        <v>74.945761404248003</v>
       </c>
       <c r="D32">
         <v>39.838268740672</v>
@@ -1949,7 +1982,7 @@
         <v>10116.39</v>
       </c>
       <c r="G32">
-        <v>11.4079</v>
+        <v>11.4636</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
@@ -1957,7 +1990,7 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>75.862969715142</v>
+        <v>76.114574146023003</v>
       </c>
       <c r="C33">
         <v>61.588411377120998</v>
@@ -1972,7 +2005,7 @@
         <v>10264.32</v>
       </c>
       <c r="G33">
-        <v>11.380699999999999</v>
+        <v>11.3942</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -1980,10 +2013,10 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>76.749865435906997</v>
+        <v>76.491140869831995</v>
       </c>
       <c r="C34">
-        <v>59.752815717141999</v>
+        <v>59.752815717139001</v>
       </c>
       <c r="D34">
         <v>40.088043180325997</v>
@@ -1995,7 +2028,7 @@
         <v>10957.37</v>
       </c>
       <c r="G34">
-        <v>11.388400000000001</v>
+        <v>11.4864</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -2003,10 +2036,10 @@
         <v>36</v>
       </c>
       <c r="B35">
-        <v>76.542400120257</v>
+        <v>77.160903447516006</v>
       </c>
       <c r="C35">
-        <v>64.657805801052007</v>
+        <v>64.657805801045001</v>
       </c>
       <c r="D35">
         <v>39.099826295804</v>
@@ -2018,7 +2051,7 @@
         <v>11564.35</v>
       </c>
       <c r="G35">
-        <v>11.539</v>
+        <v>11.398300000000001</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -2026,10 +2059,10 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>77.597182492399</v>
+        <v>77.235093879681997</v>
       </c>
       <c r="C36">
-        <v>93.311601677278006</v>
+        <v>93.311601677255993</v>
       </c>
       <c r="D36">
         <v>39.169206341328</v>
@@ -2041,7 +2074,7 @@
         <v>12102.55</v>
       </c>
       <c r="G36">
-        <v>11.237299999999999</v>
+        <v>11.3681</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -2049,10 +2082,10 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>78.613752436210007</v>
+        <v>78.083548965220004</v>
       </c>
       <c r="C37">
-        <v>93.349471308652994</v>
+        <v>93.349471308622</v>
       </c>
       <c r="D37">
         <v>41.712131922208002</v>
@@ -2064,7 +2097,7 @@
         <v>12917.88</v>
       </c>
       <c r="G37">
-        <v>11.1495</v>
+        <v>11.2041</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -2072,10 +2105,10 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>74.599199264882003</v>
+        <v>75.413723601005003</v>
       </c>
       <c r="C38">
-        <v>80.668535794415007</v>
+        <v>80.668535794380006</v>
       </c>
       <c r="D38">
         <v>42.019477188346997</v>
@@ -2087,7 +2120,7 @@
         <v>13097.12</v>
       </c>
       <c r="G38">
-        <v>11.2141</v>
+        <v>11.2607</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -2095,10 +2128,10 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>73.878798399654002</v>
+        <v>74.122589725283007</v>
       </c>
       <c r="C39">
-        <v>71.936698586107994</v>
+        <v>71.936698586074996</v>
       </c>
       <c r="D39">
         <v>43.222584660529002</v>
@@ -2110,7 +2143,7 @@
         <v>13789.46</v>
       </c>
       <c r="G39">
-        <v>11.096500000000001</v>
+        <v>11.136699999999999</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -2118,10 +2151,10 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>76.063421614120998</v>
+        <v>77.074854608140996</v>
       </c>
       <c r="C40">
-        <v>63.412448942612997</v>
+        <v>63.412448942585002</v>
       </c>
       <c r="D40">
         <v>42.862173490898002</v>
@@ -2133,7 +2166,7 @@
         <v>12676.9</v>
       </c>
       <c r="G40">
-        <v>11.1783</v>
+        <v>11.1427</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
@@ -2141,10 +2174,10 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>79.215658288664002</v>
+        <v>77.599479346221997</v>
       </c>
       <c r="C41">
-        <v>68.462732933333996</v>
+        <v>68.462732933303997</v>
       </c>
       <c r="D41">
         <v>41.124198784562999</v>
@@ -2156,7 +2189,7 @@
         <v>12322.99</v>
       </c>
       <c r="G41">
-        <v>11.0832</v>
+        <v>11.116300000000001</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -2164,10 +2197,10 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>79.088214960909994</v>
+        <v>79.350268774773994</v>
       </c>
       <c r="C42">
-        <v>77.094490972789998</v>
+        <v>77.094490972757001</v>
       </c>
       <c r="D42">
         <v>40.653950418611998</v>
@@ -2179,7 +2212,7 @@
         <v>12964.39</v>
       </c>
       <c r="G42">
-        <v>10.916</v>
+        <v>10.9733</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -2187,10 +2220,10 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>78.087974637382004</v>
+        <v>77.824628120436003</v>
       </c>
       <c r="C43">
-        <v>75.010521400529996</v>
+        <v>75.010521400505993</v>
       </c>
       <c r="D43">
         <v>41.055830727975</v>
@@ -2202,7 +2235,7 @@
         <v>13486.13</v>
       </c>
       <c r="G43">
-        <v>10.7752</v>
+        <v>10.822800000000001</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -2210,10 +2243,10 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>76.108326187998998</v>
+        <v>76.7233942095</v>
       </c>
       <c r="C44">
-        <v>80.761168050980999</v>
+        <v>80.761168050964997</v>
       </c>
       <c r="D44">
         <v>41.125404075920002</v>
@@ -2225,7 +2258,7 @@
         <v>14409.66</v>
       </c>
       <c r="G44">
-        <v>10.605700000000001</v>
+        <v>10.678100000000001</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -2233,7 +2266,7 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>78.495941868095997</v>
+        <v>77.971653802663994</v>
       </c>
       <c r="C45">
         <v>64.655984312341999</v>
@@ -2248,7 +2281,7 @@
         <v>14243.19</v>
       </c>
       <c r="G45">
-        <v>10.7995</v>
+        <v>10.6882</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -2256,10 +2289,10 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>79.097560538861998</v>
+        <v>78.723733139901995</v>
       </c>
       <c r="C46">
-        <v>59.118641916800001</v>
+        <v>59.118641916809999</v>
       </c>
       <c r="D46">
         <v>41.708963780631002</v>
@@ -2271,7 +2304,7 @@
         <v>16120.08</v>
       </c>
       <c r="G46">
-        <v>10.790699999999999</v>
+        <v>10.7775</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -2279,10 +2312,10 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>78.968514700306002</v>
+        <v>79.831450006672995</v>
       </c>
       <c r="C47">
-        <v>62.916580907632003</v>
+        <v>62.916580907655003</v>
       </c>
       <c r="D47">
         <v>41.971550838587</v>
@@ -2294,7 +2327,7 @@
         <v>15759.73</v>
       </c>
       <c r="G47">
-        <v>10.7857</v>
+        <v>10.8324</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -2302,10 +2335,10 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>80.250749880087994</v>
+        <v>79.761423403608006</v>
       </c>
       <c r="C48">
-        <v>90.476193990466996</v>
+        <v>90.476193990537993</v>
       </c>
       <c r="D48">
         <v>42.105013533792999</v>
@@ -2317,7 +2350,7 @@
         <v>16830.96</v>
       </c>
       <c r="G48">
-        <v>10.5793</v>
+        <v>10.6685</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
@@ -2325,10 +2358,10 @@
         <v>50</v>
       </c>
       <c r="B49">
-        <v>81.090409155790994</v>
+        <v>80.986013149580003</v>
       </c>
       <c r="C49">
-        <v>87.446820542042005</v>
+        <v>87.446820542137004</v>
       </c>
       <c r="D49">
         <v>44.332791536949998</v>
@@ -2340,7 +2373,7 @@
         <v>17802.71</v>
       </c>
       <c r="G49">
-        <v>10.634399999999999</v>
+        <v>10.6295</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -2348,10 +2381,10 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>79.264682642815998</v>
+        <v>79.527855735794006</v>
       </c>
       <c r="C50">
-        <v>88.651394102686993</v>
+        <v>88.651394102826998</v>
       </c>
       <c r="D50">
         <v>43.941498399982002</v>
@@ -2363,7 +2396,7 @@
         <v>18907.099999999999</v>
       </c>
       <c r="G50">
-        <v>10.443300000000001</v>
+        <v>10.547000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -2371,10 +2404,10 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>76.806691431369003</v>
+        <v>77.060243763854004</v>
       </c>
       <c r="C51">
-        <v>71.407380269420003</v>
+        <v>71.407380269531998</v>
       </c>
       <c r="D51">
         <v>43.910020768118002</v>
@@ -2386,7 +2419,7 @@
         <v>18706.32</v>
       </c>
       <c r="G51">
-        <v>10.456</v>
+        <v>10.4833</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -2394,10 +2427,10 @@
         <v>53</v>
       </c>
       <c r="B52">
-        <v>82.035547868674996</v>
+        <v>80.774608290971003</v>
       </c>
       <c r="C52">
-        <v>63.712680075127999</v>
+        <v>63.712680075221002</v>
       </c>
       <c r="D52">
         <v>45.602881088803997</v>
@@ -2409,7 +2442,7 @@
         <v>19272.63</v>
       </c>
       <c r="G52">
-        <v>10.8935</v>
+        <v>10.7468</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -2417,10 +2450,10 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>79.666903428370006</v>
+        <v>81.290226114084007</v>
       </c>
       <c r="C53">
-        <v>71.132209837158996</v>
+        <v>71.132209837274004</v>
       </c>
       <c r="D53">
         <v>44.785435891577997</v>
@@ -2432,7 +2465,7 @@
         <v>20646.189999999999</v>
       </c>
       <c r="G53">
-        <v>11.090299999999999</v>
+        <v>11.0421</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -2440,10 +2473,10 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>84.410931545875997</v>
+        <v>83.847142136372995</v>
       </c>
       <c r="C54">
-        <v>82.385425667115996</v>
+        <v>82.385425667248001</v>
       </c>
       <c r="D54">
         <v>44.650804190865003</v>
@@ -2455,7 +2488,7 @@
         <v>18677.919999999998</v>
       </c>
       <c r="G54">
-        <v>11.2966</v>
+        <v>11.0923</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -2463,10 +2496,10 @@
         <v>56</v>
       </c>
       <c r="B55">
-        <v>83.279664450918006</v>
+        <v>82.885945231118001</v>
       </c>
       <c r="C55">
-        <v>89.922489906989</v>
+        <v>89.922489907108002</v>
       </c>
       <c r="D55">
         <v>44.233933754907</v>
@@ -2478,7 +2511,7 @@
         <v>19147.169999999998</v>
       </c>
       <c r="G55">
-        <v>11.2723</v>
+        <v>11.391299999999999</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -2486,10 +2519,10 @@
         <v>57</v>
       </c>
       <c r="B56">
-        <v>80.640959297072001</v>
+        <v>81.521710544493004</v>
       </c>
       <c r="C56">
-        <v>79.947651628958994</v>
+        <v>79.947651629014999</v>
       </c>
       <c r="D56">
         <v>44.867405533193001</v>
@@ -2501,7 +2534,7 @@
         <v>20095.93</v>
       </c>
       <c r="G56">
-        <v>10.918100000000001</v>
+        <v>10.985799999999999</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -2509,10 +2542,10 @@
         <v>58</v>
       </c>
       <c r="B57">
-        <v>82.410437825767005</v>
+        <v>81.796673019235001</v>
       </c>
       <c r="C57">
-        <v>63.548550556698999</v>
+        <v>63.548550556701997</v>
       </c>
       <c r="D57">
         <v>45.038260799334999</v>
@@ -2524,7 +2557,7 @@
         <v>21049.35</v>
       </c>
       <c r="G57">
-        <v>10.903700000000001</v>
+        <v>10.872</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
@@ -2532,10 +2565,10 @@
         <v>59</v>
       </c>
       <c r="B58">
-        <v>82.162539648004994</v>
+        <v>82.168569226139994</v>
       </c>
       <c r="C58">
-        <v>59.738747503413997</v>
+        <v>59.738747503385</v>
       </c>
       <c r="D58">
         <v>45.060374418395</v>
@@ -2547,7 +2580,7 @@
         <v>21937.11</v>
       </c>
       <c r="G58">
-        <v>10.993499999999999</v>
+        <v>10.985300000000001</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -2555,10 +2588,10 @@
         <v>60</v>
       </c>
       <c r="B59">
-        <v>83.526198503125997</v>
+        <v>83.802985910401006</v>
       </c>
       <c r="C59">
-        <v>73.131364790828997</v>
+        <v>73.131364790730998</v>
       </c>
       <c r="D59">
         <v>44.301648185090997</v>
@@ -2570,7 +2603,7 @@
         <v>23046.95</v>
       </c>
       <c r="G59">
-        <v>10.763999999999999</v>
+        <v>10.8971</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
@@ -2578,10 +2611,10 @@
         <v>61</v>
       </c>
       <c r="B60">
-        <v>82.727404653711005</v>
+        <v>82.447981898874005</v>
       </c>
       <c r="C60">
-        <v>91.770544742083004</v>
+        <v>91.770544741847004</v>
       </c>
       <c r="D60">
         <v>43.188289674998003</v>
@@ -2593,7 +2626,7 @@
         <v>24962.01</v>
       </c>
       <c r="G60">
-        <v>10.9975</v>
+        <v>10.9177</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
@@ -2601,10 +2634,10 @@
         <v>62</v>
       </c>
       <c r="B61">
-        <v>82.525566409795005</v>
+        <v>83.193288885966993</v>
       </c>
       <c r="C61">
-        <v>103.250428010001</v>
+        <v>103.250428009595</v>
       </c>
       <c r="D61">
         <v>44.787074059931001</v>
@@ -2616,7 +2649,7 @@
         <v>26448.32</v>
       </c>
       <c r="G61">
-        <v>10.8116</v>
+        <v>10.847899999999999</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
@@ -2624,10 +2657,10 @@
         <v>63</v>
       </c>
       <c r="B62">
-        <v>80.898321986325996</v>
+        <v>80.357608659396007</v>
       </c>
       <c r="C62">
-        <v>85.252024684313</v>
+        <v>85.252024683873998</v>
       </c>
       <c r="D62">
         <v>42.741221973401998</v>
@@ -2639,7 +2672,7 @@
         <v>27561.49</v>
       </c>
       <c r="G62">
-        <v>11.0382</v>
+        <v>10.9529</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
@@ -2647,10 +2680,10 @@
         <v>64</v>
       </c>
       <c r="B63">
-        <v>78.349341712959003</v>
+        <v>78.607327960397001</v>
       </c>
       <c r="C63">
-        <v>76.785520578988994</v>
+        <v>76.785520578559002</v>
       </c>
       <c r="D63">
         <v>42.377794728391002</v>
@@ -2662,7 +2695,7 @@
         <v>26638.95</v>
       </c>
       <c r="G63">
-        <v>11.168200000000001</v>
+        <v>10.9998</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
@@ -2670,10 +2703,10 @@
         <v>65</v>
       </c>
       <c r="B64">
-        <v>83.830294412173004</v>
+        <v>82.995189302621995</v>
       </c>
       <c r="C64">
-        <v>70.310842174602001</v>
+        <v>70.310842174230999</v>
       </c>
       <c r="D64">
         <v>43.567732769547</v>
@@ -2685,7 +2718,7 @@
         <v>28747.69</v>
       </c>
       <c r="G64">
-        <v>11.0322</v>
+        <v>11.113899999999999</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
@@ -2693,10 +2726,10 @@
         <v>66</v>
       </c>
       <c r="B65">
-        <v>81.968037121150005</v>
+        <v>83.300659920235006</v>
       </c>
       <c r="C65">
-        <v>73.656864302887996</v>
+        <v>73.656864302490007</v>
       </c>
       <c r="D65">
         <v>43.441486719152998</v>
@@ -2708,7 +2741,7 @@
         <v>28996.71</v>
       </c>
       <c r="G65">
-        <v>10.9278</v>
+        <v>10.980600000000001</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -2716,10 +2749,10 @@
         <v>67</v>
       </c>
       <c r="B66">
-        <v>85.634108480392996</v>
+        <v>84.996678768707</v>
       </c>
       <c r="C66">
-        <v>86.272158228307006</v>
+        <v>86.272158227838005</v>
       </c>
       <c r="D66">
         <v>43.753407724589003</v>
@@ -2731,7 +2764,7 @@
         <v>31398.959999999999</v>
       </c>
       <c r="G66">
-        <v>10.7445</v>
+        <v>10.816700000000001</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -2739,10 +2772,10 @@
         <v>68</v>
       </c>
       <c r="B67">
-        <v>84.987967020260996</v>
+        <v>84.993760712135</v>
       </c>
       <c r="C67">
-        <v>97.299091900625996</v>
+        <v>97.299091900175</v>
       </c>
       <c r="D67">
         <v>43.069396217955997</v>
@@ -2754,7 +2787,7 @@
         <v>31151.05</v>
       </c>
       <c r="G67">
-        <v>10.794600000000001</v>
+        <v>10.835000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -2762,10 +2795,10 @@
         <v>69</v>
       </c>
       <c r="B68">
-        <v>83.281569462015</v>
+        <v>83.558176766396002</v>
       </c>
       <c r="C68">
-        <v>84.691700335885002</v>
+        <v>84.691700335684004</v>
       </c>
       <c r="D68">
         <v>42.962881260261</v>
@@ -2777,7 +2810,7 @@
         <v>30659.66</v>
       </c>
       <c r="G68">
-        <v>10.927300000000001</v>
+        <v>10.8109</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -2785,10 +2818,10 @@
         <v>70</v>
       </c>
       <c r="B69">
-        <v>84.276007671391</v>
+        <v>83.707344399125006</v>
       </c>
       <c r="C69">
-        <v>68.968552660897998</v>
+        <v>68.968552660894005</v>
       </c>
       <c r="D69">
         <v>43.986291684984003</v>
@@ -2800,7 +2833,7 @@
         <v>30347.86</v>
       </c>
       <c r="G69">
-        <v>11.037800000000001</v>
+        <v>11.0456</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -2808,10 +2841,10 @@
         <v>71</v>
       </c>
       <c r="B70">
-        <v>83.266925789116996</v>
+        <v>84.225485012394003</v>
       </c>
       <c r="C70">
-        <v>60.541983374135</v>
+        <v>60.541983374245</v>
       </c>
       <c r="D70">
         <v>43.023769283466002</v>
@@ -2823,7 +2856,7 @@
         <v>30296.19</v>
       </c>
       <c r="G70">
-        <v>10.9315</v>
+        <v>11.031499999999999</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -2831,10 +2864,10 @@
         <v>72</v>
       </c>
       <c r="B71">
-        <v>86.593980036599007</v>
+        <v>86.015559893344005</v>
       </c>
       <c r="C71">
-        <v>76.787795457783005</v>
+        <v>76.787795458158996</v>
       </c>
       <c r="D71">
         <v>41.266570387477998</v>
@@ -2846,7 +2879,7 @@
         <v>31458.67</v>
       </c>
       <c r="G71">
-        <v>10.702299999999999</v>
+        <v>10.8231</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
@@ -2854,10 +2887,10 @@
         <v>73</v>
       </c>
       <c r="B72">
-        <v>84.785025565423993</v>
+        <v>84.383824044432998</v>
       </c>
       <c r="C72">
-        <v>106.57165683567</v>
+        <v>106.571656836751</v>
       </c>
       <c r="D72">
         <v>40.856834279973</v>
@@ -2869,7 +2902,7 @@
         <v>29770.52</v>
       </c>
       <c r="G72">
-        <v>10.896800000000001</v>
+        <v>10.8866</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
@@ -2877,10 +2910,10 @@
         <v>74</v>
       </c>
       <c r="B73">
-        <v>83.550798978242995</v>
+        <v>84.463491743690994</v>
       </c>
       <c r="C73">
-        <v>89.805964525909005</v>
+        <v>89.805964527103995</v>
       </c>
       <c r="D73">
         <v>42.820180786066999</v>
@@ -2892,7 +2925,7 @@
         <v>29536.83</v>
       </c>
       <c r="G73">
-        <v>10.915699999999999</v>
+        <v>10.8484</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
@@ -2900,10 +2933,10 @@
         <v>75</v>
       </c>
       <c r="B74">
-        <v>82.477617804828</v>
+        <v>81.864166937028003</v>
       </c>
       <c r="C74">
-        <v>87.999415912141998</v>
+        <v>87.999415913834</v>
       </c>
       <c r="D74">
         <v>42.182214698816999</v>
@@ -2915,7 +2948,7 @@
         <v>28793.64</v>
       </c>
       <c r="G74">
-        <v>10.8262</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
@@ -2923,10 +2956,10 @@
         <v>76</v>
       </c>
       <c r="B75">
-        <v>81.216819355908996</v>
+        <v>80.146601325516002</v>
       </c>
       <c r="C75">
-        <v>75.896374248388994</v>
+        <v>75.896374249906998</v>
       </c>
       <c r="D75">
         <v>41.220788409099001</v>
@@ -2938,7 +2971,7 @@
         <v>28918.52</v>
       </c>
       <c r="G75">
-        <v>10.724299999999999</v>
+        <v>10.766500000000001</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
@@ -2946,10 +2979,10 @@
         <v>77</v>
       </c>
       <c r="B76">
-        <v>80.733070849729998</v>
+        <v>83.320527023672994</v>
       </c>
       <c r="C76">
-        <v>66.348516824680004</v>
+        <v>66.348516825898997</v>
       </c>
       <c r="D76">
         <v>41.896449634047997</v>
@@ -2961,7 +2994,7 @@
         <v>30912.99</v>
       </c>
       <c r="G76">
-        <v>10.648199999999999</v>
+        <v>10.731299999999999</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
@@ -2969,10 +3002,10 @@
         <v>78</v>
       </c>
       <c r="B77">
-        <v>86.804123598795002</v>
+        <v>84.508159419205001</v>
       </c>
       <c r="C77">
-        <v>77.379843454153004</v>
+        <v>77.379843455783003</v>
       </c>
       <c r="D77">
         <v>40.153081011391997</v>
@@ -2984,7 +3017,7 @@
         <v>30281.41</v>
       </c>
       <c r="G77">
-        <v>10.509499999999999</v>
+        <v>10.5154</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
@@ -2992,10 +3025,10 @@
         <v>79</v>
       </c>
       <c r="B78">
-        <v>85.475304853099004</v>
+        <v>85.365389985945995</v>
       </c>
       <c r="C78">
-        <v>91.372117726537994</v>
+        <v>91.372117728459003</v>
       </c>
       <c r="D78">
         <v>38.911996368962001</v>
@@ -3007,7 +3040,7 @@
         <v>31975.47</v>
       </c>
       <c r="G78">
-        <v>10.3306</v>
+        <v>10.4352</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
@@ -3015,10 +3048,10 @@
         <v>80</v>
       </c>
       <c r="B79">
-        <v>85.477209603044003</v>
+        <v>86.112085865400999</v>
       </c>
       <c r="C79">
-        <v>95.055841819657999</v>
+        <v>95.055841821271002</v>
       </c>
       <c r="D79">
         <v>37.690265007720001</v>
@@ -3030,7 +3063,7 @@
         <v>29395.49</v>
       </c>
       <c r="G79">
-        <v>10.306900000000001</v>
+        <v>10.3292</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -3038,10 +3071,10 @@
         <v>81</v>
       </c>
       <c r="B80">
-        <v>85.630971218623003</v>
+        <v>84.993701095863003</v>
       </c>
       <c r="C80">
-        <v>90.394399227644001</v>
+        <v>90.394399228504994</v>
       </c>
       <c r="D80">
         <v>36.703523097359998</v>
@@ -3053,7 +3086,7 @@
         <v>27501.02</v>
       </c>
       <c r="G80">
-        <v>10.035299999999999</v>
+        <v>10.2155</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
@@ -3061,10 +3094,10 @@
         <v>82</v>
       </c>
       <c r="B81">
-        <v>83.082533530722998</v>
+        <v>83.754792677614006</v>
       </c>
       <c r="C81">
-        <v>61.858347291694997</v>
+        <v>61.858347291721998</v>
       </c>
       <c r="D81">
         <v>37.261608880235997</v>
@@ -3076,7 +3109,7 @@
         <v>26290.99</v>
       </c>
       <c r="G81">
-        <v>10.284700000000001</v>
+        <v>10.109500000000001</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
@@ -3084,10 +3117,10 @@
         <v>83</v>
       </c>
       <c r="B82">
-        <v>84.120378723155</v>
+        <v>83.727671136240005</v>
       </c>
       <c r="C82">
-        <v>57.816346721609001</v>
+        <v>57.816346721294003</v>
       </c>
       <c r="D82">
         <v>36.655757017577002</v>
@@ -3099,7 +3132,7 @@
         <v>24888.9</v>
       </c>
       <c r="G82">
-        <v>10.981400000000001</v>
+        <v>10.643700000000001</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
@@ -3107,10 +3140,10 @@
         <v>84</v>
       </c>
       <c r="B83">
-        <v>86.631648828918003</v>
+        <v>86.047447197126999</v>
       </c>
       <c r="C83">
-        <v>78.227051298358006</v>
+        <v>78.227051297000997</v>
       </c>
       <c r="D83">
         <v>34.207808884236997</v>
@@ -3122,7 +3155,7 @@
         <v>20445.32</v>
       </c>
       <c r="G83">
-        <v>12.7125</v>
+        <v>12.631399999999999</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
@@ -3130,10 +3163,10 @@
         <v>85</v>
       </c>
       <c r="B84">
-        <v>82.903974708871999</v>
+        <v>83.858306525605002</v>
       </c>
       <c r="C84">
-        <v>101.098076249888</v>
+        <v>101.098076246381</v>
       </c>
       <c r="D84">
         <v>34.949981333476998</v>
@@ -3145,7 +3178,7 @@
         <v>20534.72</v>
       </c>
       <c r="G84">
-        <v>13.3225</v>
+        <v>13.114000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
@@ -3153,10 +3186,10 @@
         <v>86</v>
       </c>
       <c r="B85">
-        <v>83.155772885903005</v>
+        <v>82.600525423134002</v>
       </c>
       <c r="C85">
-        <v>103.044140530856</v>
+        <v>103.044140525554</v>
       </c>
       <c r="D85">
         <v>34.998662925250997</v>
@@ -3168,7 +3201,7 @@
         <v>22380.32</v>
       </c>
       <c r="G85">
-        <v>13.8325</v>
+        <v>13.422599999999999</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
@@ -3176,10 +3209,10 @@
         <v>87</v>
       </c>
       <c r="B86">
-        <v>76.019281324613999</v>
+        <v>75.921516014526006</v>
       </c>
       <c r="C86">
-        <v>86.909367986126995</v>
+        <v>86.909367980316006</v>
       </c>
       <c r="D86">
         <v>34.408357698124</v>
@@ -3191,7 +3224,7 @@
         <v>19565.14</v>
       </c>
       <c r="G86">
-        <v>14.309699999999999</v>
+        <v>13.892099999999999</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -3199,10 +3232,10 @@
         <v>88</v>
       </c>
       <c r="B87">
-        <v>73.650563402428006</v>
+        <v>73.893837976377995</v>
       </c>
       <c r="C87">
-        <v>69.852838483374995</v>
+        <v>69.852838478915999</v>
       </c>
       <c r="D87">
         <v>33.402302324951002</v>
@@ -3214,7 +3247,7 @@
         <v>17752.18</v>
       </c>
       <c r="G87">
-        <v>15.069800000000001</v>
+        <v>14.5966</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -3222,10 +3255,10 @@
         <v>89</v>
       </c>
       <c r="B88">
-        <v>78.418479865766002</v>
+        <v>77.994558705204994</v>
       </c>
       <c r="C88">
-        <v>69.072561851474006</v>
+        <v>69.072561846941994</v>
       </c>
       <c r="D88">
         <v>33.472771550429002</v>
@@ -3237,7 +3270,7 @@
         <v>19626.75</v>
       </c>
       <c r="G88">
-        <v>14.1517</v>
+        <v>14.669499999999999</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
@@ -3245,10 +3278,10 @@
         <v>90</v>
       </c>
       <c r="B89">
-        <v>76.256850123282007</v>
+        <v>76.665811279644004</v>
       </c>
       <c r="C89">
-        <v>79.097808367921004</v>
+        <v>79.097808362128006</v>
       </c>
       <c r="D89">
         <v>34.600273054943997</v>
@@ -3260,7 +3293,7 @@
         <v>21898.85</v>
       </c>
       <c r="G89">
-        <v>13.8443</v>
+        <v>13.4367</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -3268,10 +3301,10 @@
         <v>91</v>
       </c>
       <c r="B90">
-        <v>76.803582114137001</v>
+        <v>77.425021927608</v>
       </c>
       <c r="C90">
-        <v>85.142161796170996</v>
+        <v>85.142161790393999</v>
       </c>
       <c r="D90">
         <v>33.193280715325002</v>
@@ -3283,7 +3316,7 @@
         <v>24331.71</v>
       </c>
       <c r="G90">
-        <v>13.166700000000001</v>
+        <v>13.162100000000001</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -3291,10 +3324,10 @@
         <v>92</v>
       </c>
       <c r="B91">
-        <v>79.089878704222002</v>
+        <v>78.721130648659994</v>
       </c>
       <c r="C91">
-        <v>93.811789458378001</v>
+        <v>93.811789453117001</v>
       </c>
       <c r="D91">
         <v>34.225594932537</v>
@@ -3306,7 +3339,7 @@
         <v>24368.38</v>
       </c>
       <c r="G91">
-        <v>13.1722</v>
+        <v>13.341799999999999</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
@@ -3314,10 +3347,10 @@
         <v>93</v>
       </c>
       <c r="B92">
-        <v>80.181038260516004</v>
+        <v>79.639975571530002</v>
       </c>
       <c r="C92">
-        <v>83.663976343640996</v>
+        <v>83.663976341307006</v>
       </c>
       <c r="D92">
         <v>36.050174206744998</v>
@@ -3329,7 +3362,7 @@
         <v>27043.5</v>
       </c>
       <c r="G92">
-        <v>13.2125</v>
+        <v>13.365399999999999</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
@@ -3337,10 +3370,10 @@
         <v>94</v>
       </c>
       <c r="B93">
-        <v>78.071588129535996</v>
+        <v>78.924653533929998</v>
       </c>
       <c r="C93">
-        <v>62.648172813835998</v>
+        <v>62.648172813909</v>
       </c>
       <c r="D93">
         <v>34.530559234720997</v>
@@ -3352,7 +3385,7 @@
         <v>28129.95</v>
       </c>
       <c r="G93">
-        <v>13.314</v>
+        <v>13.007999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -3360,10 +3393,10 @@
         <v>95</v>
       </c>
       <c r="B94">
-        <v>80.063889370865994</v>
+        <v>79.575564209624005</v>
       </c>
       <c r="C94">
-        <v>58.973530331021998</v>
+        <v>58.973530332281001</v>
       </c>
       <c r="D94">
         <v>34.499310914771002</v>
@@ -3375,7 +3408,7 @@
         <v>29232.240000000002</v>
       </c>
       <c r="G94">
-        <v>13.492800000000001</v>
+        <v>13.421200000000001</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
@@ -3383,10 +3416,10 @@
         <v>96</v>
       </c>
       <c r="B95">
-        <v>82.344494798328</v>
+        <v>82.238405065840993</v>
       </c>
       <c r="C95">
-        <v>71.753008910155998</v>
+        <v>71.753008914233007</v>
       </c>
       <c r="D95">
         <v>32.609581622264002</v>
@@ -3398,7 +3431,7 @@
         <v>28646.03</v>
       </c>
       <c r="G95">
-        <v>13.1479</v>
+        <v>13.2257</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -3406,10 +3439,10 @@
         <v>97</v>
       </c>
       <c r="B96">
-        <v>82.196433201740007</v>
+        <v>82.806708351867002</v>
       </c>
       <c r="C96">
-        <v>98.646229525851993</v>
+        <v>98.646229537655003</v>
       </c>
       <c r="D96">
         <v>33.170739517975001</v>
@@ -3421,7 +3454,7 @@
         <v>30957.11</v>
       </c>
       <c r="G96">
-        <v>12.915699999999999</v>
+        <v>13.109400000000001</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
@@ -3429,10 +3462,10 @@
         <v>98</v>
       </c>
       <c r="B97">
-        <v>83.291762364402999</v>
+        <v>82.672108835312997</v>
       </c>
       <c r="C97">
-        <v>98.581987347177005</v>
+        <v>98.581987363931006</v>
       </c>
       <c r="D97">
         <v>33.986489860492</v>
@@ -3444,7 +3477,7 @@
         <v>32120.47</v>
       </c>
       <c r="G97">
-        <v>13.065899999999999</v>
+        <v>12.863099999999999</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
@@ -3452,10 +3485,10 @@
         <v>99</v>
       </c>
       <c r="B98">
-        <v>77.817791548499002</v>
+        <v>78.447220930715005</v>
       </c>
       <c r="C98">
-        <v>78.358912136002004</v>
+        <v>78.358912151878002</v>
       </c>
       <c r="D98">
         <v>34.801952208933002</v>
@@ -3467,7 +3500,7 @@
         <v>30391.61</v>
       </c>
       <c r="G98">
-        <v>13.0098</v>
+        <v>12.8019</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
@@ -3475,10 +3508,10 @@
         <v>100</v>
       </c>
       <c r="B99">
-        <v>77.042083581214001</v>
+        <v>77.296018592769997</v>
       </c>
       <c r="C99">
-        <v>74.848797459638007</v>
+        <v>74.848797476792996</v>
       </c>
       <c r="D99">
         <v>34.258568869686002</v>
@@ -3490,7 +3523,7 @@
         <v>31634.54</v>
       </c>
       <c r="G99">
-        <v>12.776899999999999</v>
+        <v>12.942399999999999</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
@@ -3498,10 +3531,10 @@
         <v>101</v>
       </c>
       <c r="B100">
-        <v>83.847590781728002</v>
+        <v>82.564368161161994</v>
       </c>
       <c r="C100">
-        <v>67.694859275629</v>
+        <v>67.694859290132996</v>
       </c>
       <c r="D100">
         <v>34.669094444700001</v>
@@ -3513,7 +3546,7 @@
         <v>33266.43</v>
       </c>
       <c r="G100">
-        <v>12.3306</v>
+        <v>12.573700000000001</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
@@ -3521,10 +3554,10 @@
         <v>102</v>
       </c>
       <c r="B101">
-        <v>82.217903937654995</v>
+        <v>82.546060547216001</v>
       </c>
       <c r="C101">
-        <v>84.177665688112</v>
+        <v>84.177665710320994</v>
       </c>
       <c r="D101">
         <v>35.036058935423</v>
@@ -3536,7 +3569,7 @@
         <v>32687.32</v>
       </c>
       <c r="G101">
-        <v>12.262600000000001</v>
+        <v>12.2302</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -3544,10 +3577,10 @@
         <v>103</v>
       </c>
       <c r="B102">
-        <v>82.731904810404004</v>
+        <v>83.635547138142996</v>
       </c>
       <c r="C102">
-        <v>93.927245431374004</v>
+        <v>93.927245454949997</v>
       </c>
       <c r="D102">
         <v>35.593787418353003</v>
@@ -3559,7 +3592,7 @@
         <v>32038.53</v>
       </c>
       <c r="G102">
-        <v>12.9146</v>
+        <v>12.742800000000001</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -3567,10 +3600,10 @@
         <v>104</v>
       </c>
       <c r="B103">
-        <v>84.096843547874997</v>
+        <v>83.583960623210004</v>
       </c>
       <c r="C103">
-        <v>95.324306317098007</v>
+        <v>95.324306335537003</v>
       </c>
       <c r="D103">
         <v>36.779916995592998</v>
@@ -3582,7 +3615,7 @@
         <v>31156.97</v>
       </c>
       <c r="G103">
-        <v>12.844099999999999</v>
+        <v>12.7193</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
@@ -3590,10 +3623,10 @@
         <v>105</v>
       </c>
       <c r="B104">
-        <v>83.780237705675006</v>
+        <v>83.672563591957996</v>
       </c>
       <c r="C104">
-        <v>88.868066237196999</v>
+        <v>88.868066246189002</v>
       </c>
       <c r="D104">
         <v>36.927883087241</v>
@@ -3605,7 +3638,7 @@
         <v>32308.74</v>
       </c>
       <c r="G104">
-        <v>12.6455</v>
+        <v>12.818899999999999</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
@@ -3613,10 +3646,10 @@
         <v>106</v>
       </c>
       <c r="B105">
-        <v>82.859897309326996</v>
+        <v>83.134777345207993</v>
       </c>
       <c r="C105">
-        <v>65.733078089390006</v>
+        <v>65.733078089106996</v>
       </c>
       <c r="D105">
         <v>37.200570089579998</v>
@@ -3628,7 +3661,7 @@
         <v>31679.85</v>
       </c>
       <c r="G105">
-        <v>13.1676</v>
+        <v>12.769500000000001</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -3636,10 +3669,10 @@
         <v>107</v>
       </c>
       <c r="B106">
-        <v>83.531292265076004</v>
+        <v>83.249270201927004</v>
       </c>
       <c r="C106">
-        <v>65.647687095191003</v>
+        <v>65.647687089574006</v>
       </c>
       <c r="D106">
         <v>38.33026169163</v>
@@ -3651,7 +3684,7 @@
         <v>33330.339999999997</v>
       </c>
       <c r="G106">
-        <v>12.5998</v>
+        <v>12.7997</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
@@ -3659,10 +3692,10 @@
         <v>108</v>
       </c>
       <c r="B107">
-        <v>84.516498317832998</v>
+        <v>85.199379631707998</v>
       </c>
       <c r="C107">
-        <v>73.613893384630003</v>
+        <v>73.613893369595999</v>
       </c>
       <c r="D107">
         <v>37.408578165013999</v>
@@ -3674,7 +3707,7 @@
         <v>35568.22</v>
       </c>
       <c r="G107">
-        <v>12.338699999999999</v>
+        <v>12.4374</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.2">
@@ -3682,10 +3715,10 @@
         <v>109</v>
       </c>
       <c r="B108">
-        <v>86.268243494773998</v>
+        <v>85.865653038293004</v>
       </c>
       <c r="C108">
-        <v>101.65961890646</v>
+        <v>101.65961886200201</v>
       </c>
       <c r="D108">
         <v>37.177350050835003</v>
@@ -3697,7 +3730,7 @@
         <v>36817.32</v>
       </c>
       <c r="G108">
-        <v>12.4664</v>
+        <v>12.3391</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.2">
@@ -3705,10 +3738,10 @@
         <v>110</v>
       </c>
       <c r="B109">
-        <v>86.361908658581996</v>
+        <v>85.779269032670001</v>
       </c>
       <c r="C109">
-        <v>93.547834776856007</v>
+        <v>93.547834721498006</v>
       </c>
       <c r="D109">
         <v>38.176654187144997</v>
@@ -3720,7 +3753,7 @@
         <v>38550.79</v>
       </c>
       <c r="G109">
-        <v>12.349600000000001</v>
+        <v>12.388500000000001</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
@@ -3728,10 +3761,10 @@
         <v>111</v>
       </c>
       <c r="B110">
-        <v>81.059540333585005</v>
+        <v>81.945286600323001</v>
       </c>
       <c r="C110">
-        <v>79.408239553841</v>
+        <v>79.408239492665999</v>
       </c>
       <c r="D110">
         <v>38.462362621981001</v>
@@ -3743,7 +3776,7 @@
         <v>36982.239999999998</v>
       </c>
       <c r="G110">
-        <v>12.151899999999999</v>
+        <v>12.1258</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.2">
@@ -3751,10 +3784,10 @@
         <v>112</v>
       </c>
       <c r="B111">
-        <v>80.115614906427993</v>
+        <v>80.380154014412</v>
       </c>
       <c r="C111">
-        <v>70.907182713568005</v>
+        <v>70.907182655789001</v>
       </c>
       <c r="D111">
         <v>38.441310674972001</v>
@@ -3766,7 +3799,7 @@
         <v>37019.699999999997</v>
       </c>
       <c r="G111">
-        <v>12.106199999999999</v>
+        <v>12.0703</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.2">
@@ -3774,10 +3807,10 @@
         <v>113</v>
       </c>
       <c r="B112">
-        <v>87.173673942253004</v>
+        <v>85.773559683469003</v>
       </c>
       <c r="C112">
-        <v>73.788636364672001</v>
+        <v>73.788636298667001</v>
       </c>
       <c r="D112">
         <v>38.323262246935002</v>
@@ -3789,7 +3822,7 @@
         <v>37440.51</v>
       </c>
       <c r="G112">
-        <v>11.9084</v>
+        <v>11.9992</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.2">
@@ -3797,10 +3830,10 @@
         <v>114</v>
       </c>
       <c r="B113">
-        <v>82.957170323216005</v>
+        <v>83.689647829465997</v>
       </c>
       <c r="C113">
-        <v>74.688351123885994</v>
+        <v>74.68835105558</v>
       </c>
       <c r="D113">
         <v>37.626520746848001</v>
@@ -3812,7 +3845,7 @@
         <v>36962.620000000003</v>
       </c>
       <c r="G113">
-        <v>11.527799999999999</v>
+        <v>11.718400000000001</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.2">
@@ -3820,10 +3853,10 @@
         <v>115</v>
       </c>
       <c r="B114">
-        <v>86.038631757133004</v>
+        <v>86.324319430417006</v>
       </c>
       <c r="C114">
-        <v>84.999197686502995</v>
+        <v>84.999197608819003</v>
       </c>
       <c r="D114">
         <v>37.359706575395002</v>
@@ -3835,7 +3868,7 @@
         <v>35832.79</v>
       </c>
       <c r="G114">
-        <v>11.577999999999999</v>
+        <v>11.6533</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.2">
@@ -3843,10 +3876,10 @@
         <v>116</v>
       </c>
       <c r="B115">
-        <v>86.875162948750997</v>
+        <v>86.581991701193999</v>
       </c>
       <c r="C115">
-        <v>81.449653210389997</v>
+        <v>81.449653154098996</v>
       </c>
       <c r="D115">
         <v>38.767404368535999</v>
@@ -3858,7 +3891,7 @@
         <v>36558.07</v>
       </c>
       <c r="G115">
-        <v>11.723000000000001</v>
+        <v>11.805999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.2">
@@ -3866,10 +3899,10 @@
         <v>117</v>
       </c>
       <c r="B116">
-        <v>86.130939632354995</v>
+        <v>86.827438201744997</v>
       </c>
       <c r="C116">
-        <v>86.846025452535997</v>
+        <v>86.846025413825004</v>
       </c>
       <c r="D116">
         <v>39.753703316429998</v>
@@ -3881,7 +3914,7 @@
         <v>35999.339999999997</v>
       </c>
       <c r="G116">
-        <v>11.7425</v>
+        <v>11.672599999999999</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.2">
@@ -3889,10 +3922,10 @@
         <v>118</v>
       </c>
       <c r="B117">
-        <v>87.289965518450998</v>
+        <v>86.706910676144005</v>
       </c>
       <c r="C117">
-        <v>69.141855916387001</v>
+        <v>69.141855912205997</v>
       </c>
       <c r="D117">
         <v>38.902257492951001</v>
@@ -3904,7 +3937,7 @@
         <v>35721.1</v>
       </c>
       <c r="G117">
-        <v>12.348000000000001</v>
+        <v>12.2319</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.2">
@@ -3912,10 +3945,10 @@
         <v>119</v>
       </c>
       <c r="B118">
-        <v>86.729544982625001</v>
+        <v>86.319620916125004</v>
       </c>
       <c r="C118">
-        <v>63.564331574529</v>
+        <v>63.564331588607999</v>
       </c>
       <c r="D118">
         <v>38.482258123392</v>
@@ -3927,7 +3960,7 @@
         <v>33503.279999999999</v>
       </c>
       <c r="G118">
-        <v>13.7994</v>
+        <v>13.044499999999999</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.2">
@@ -3935,10 +3968,10 @@
         <v>120</v>
       </c>
       <c r="B119">
-        <v>87.547271220408007</v>
+        <v>88.503133555372003</v>
       </c>
       <c r="C119">
-        <v>73.621625334640001</v>
+        <v>73.621625383430001</v>
       </c>
       <c r="D119">
         <v>37.709374678644998</v>
@@ -3950,7 +3983,7 @@
         <v>36159.99</v>
       </c>
       <c r="G119">
-        <v>13.180199999999999</v>
+        <v>13.435</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.2">
@@ -3958,10 +3991,10 @@
         <v>121</v>
       </c>
       <c r="B120">
-        <v>90.786459870936</v>
+        <v>90.232153931040997</v>
       </c>
       <c r="C120">
-        <v>100.817286384862</v>
+        <v>100.81728653667101</v>
       </c>
       <c r="D120">
         <v>37.423838980920998</v>
@@ -3973,7 +4006,7 @@
         <v>36829.15</v>
       </c>
       <c r="G120">
-        <v>13.61</v>
+        <v>13.699299999999999</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.2">
@@ -3981,10 +4014,10 @@
         <v>122</v>
       </c>
       <c r="B121">
-        <v>89.206822396958003</v>
+        <v>89.092604205631005</v>
       </c>
       <c r="C121">
-        <v>98.930386416583005</v>
+        <v>98.930386632034995</v>
       </c>
       <c r="D121">
         <v>37.714854775456999</v>
@@ -3996,7 +4029,7 @@
         <v>37077.519999999997</v>
       </c>
       <c r="G121">
-        <v>13.9476</v>
+        <v>13.7689</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.2">
@@ -4004,10 +4037,10 @@
         <v>123</v>
       </c>
       <c r="B122">
-        <v>85.357613163061004</v>
+        <v>85.641061122764</v>
       </c>
       <c r="C122">
-        <v>80.477267467486001</v>
+        <v>80.477267695711006</v>
       </c>
       <c r="D122">
         <v>39.360421363222997</v>
@@ -4019,7 +4052,7 @@
         <v>37422.68</v>
       </c>
       <c r="G122">
-        <v>13.0077</v>
+        <v>13.4178</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.2">
@@ -4027,10 +4060,10 @@
         <v>124</v>
       </c>
       <c r="B123">
-        <v>85.296764781077002</v>
+        <v>84.287757634027002</v>
       </c>
       <c r="C123">
-        <v>75.662665909097996</v>
+        <v>75.662666145714994</v>
       </c>
       <c r="D123">
         <v>38.980432396401</v>
@@ -4042,7 +4075,7 @@
         <v>37816.69</v>
       </c>
       <c r="G123">
-        <v>12.789099999999999</v>
+        <v>12.783099999999999</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.2">
@@ -4050,10 +4083,10 @@
         <v>125</v>
       </c>
       <c r="B124">
-        <v>90.120110958791003</v>
+        <v>89.222551114783997</v>
       </c>
       <c r="C124">
-        <v>75.991521730770998</v>
+        <v>75.991521981372998</v>
       </c>
       <c r="D124">
         <v>38.875000703174997</v>
@@ -4065,7 +4098,7 @@
         <v>39521.24</v>
       </c>
       <c r="G124">
-        <v>12.8093</v>
+        <v>12.7567</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.2">
@@ -4073,10 +4106,10 @@
         <v>126</v>
       </c>
       <c r="B125">
-        <v>86.670871276187</v>
+        <v>88.080122681372004</v>
       </c>
       <c r="C125">
-        <v>80.497306683873006</v>
+        <v>80.497306965934996</v>
       </c>
       <c r="D125">
         <v>40.224532607652002</v>
@@ -4088,7 +4121,7 @@
         <v>39461</v>
       </c>
       <c r="G125">
-        <v>12.994199999999999</v>
+        <v>13.069699999999999</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.2">
@@ -4096,10 +4129,10 @@
         <v>127</v>
       </c>
       <c r="B126">
-        <v>90.125978091285006</v>
+        <v>89.455247573492997</v>
       </c>
       <c r="C126">
-        <v>89.433391139674001</v>
+        <v>89.433391441550995</v>
       </c>
       <c r="D126">
         <v>39.732253561534002</v>
@@ -4111,7 +4144,7 @@
         <v>37872.949999999997</v>
       </c>
       <c r="G126">
-        <v>14.3047</v>
+        <v>13.663399999999999</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.2">
@@ -4119,10 +4152,10 @@
         <v>128</v>
       </c>
       <c r="B127">
-        <v>89.788374193237999</v>
+        <v>89.794086068870996</v>
       </c>
       <c r="C127">
-        <v>101.756729496677</v>
+        <v>101.75672980009401</v>
       </c>
       <c r="D127">
         <v>39.713253382883003</v>
@@ -4134,7 +4167,7 @@
         <v>40199.550000000003</v>
       </c>
       <c r="G127">
-        <v>13.4084</v>
+        <v>13.9192</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.2">
@@ -4142,10 +4175,10 @@
         <v>129</v>
       </c>
       <c r="B128">
-        <v>89.914964086487004</v>
+        <v>90.213172881901002</v>
       </c>
       <c r="C128">
-        <v>89.981739491802003</v>
+        <v>89.981739637855</v>
       </c>
       <c r="D128">
         <v>41.147825546828003</v>
@@ -4157,7 +4190,7 @@
         <v>40704.28</v>
       </c>
       <c r="G128">
-        <v>13.283300000000001</v>
+        <v>13.366099999999999</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
@@ -4165,10 +4198,10 @@
         <v>130</v>
       </c>
       <c r="B129">
-        <v>89.448408857274998</v>
+        <v>88.844446127165</v>
       </c>
       <c r="C129">
-        <v>71.178942010791005</v>
+        <v>71.178942023719003</v>
       </c>
       <c r="D129">
         <v>40.783200354222998</v>
@@ -4180,7 +4213,7 @@
         <v>39421.65</v>
       </c>
       <c r="G129">
-        <v>13.257099999999999</v>
+        <v>13.1845</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.2">
@@ -4188,10 +4221,10 @@
         <v>131</v>
       </c>
       <c r="B130">
-        <v>87.314056911435003</v>
+        <v>88.319069960155005</v>
       </c>
       <c r="C130">
-        <v>60.127363883280999</v>
+        <v>60.127363836363998</v>
       </c>
       <c r="D130">
         <v>39.355022500154</v>
@@ -4203,7 +4236,7 @@
         <v>40866.959999999999</v>
       </c>
       <c r="G130">
-        <v>12.8695</v>
+        <v>12.939399999999999</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
@@ -4211,10 +4244,10 @@
         <v>132</v>
       </c>
       <c r="B131">
-        <v>91.364216660056002</v>
+        <v>90.753696723738997</v>
       </c>
       <c r="C131">
-        <v>75.573902615695999</v>
+        <v>75.573902425523002</v>
       </c>
       <c r="D131">
         <v>39.629339806128002</v>
@@ -4226,7 +4259,7 @@
         <v>41619.96</v>
       </c>
       <c r="G131">
-        <v>13.091100000000001</v>
+        <v>12.891</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.2">
@@ -4234,10 +4267,10 @@
         <v>133</v>
       </c>
       <c r="B132">
-        <v>93.410554529875</v>
+        <v>92.969008525264002</v>
       </c>
       <c r="C132">
-        <v>112.927838947151</v>
+        <v>112.927838291199</v>
       </c>
       <c r="D132">
         <v>39.121394785678</v>
@@ -4249,7 +4282,7 @@
         <v>41833.519999999997</v>
       </c>
       <c r="G132">
-        <v>12.9268</v>
+        <v>13.0746</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.2">
@@ -4257,10 +4290,10 @@
         <v>134</v>
       </c>
       <c r="B133">
-        <v>90.418160143544995</v>
+        <v>91.405488820971996</v>
       </c>
       <c r="C133">
-        <v>106.169893500814</v>
+        <v>106.169892632078</v>
       </c>
       <c r="D133">
         <v>41.139502632716002</v>
@@ -4272,7 +4305,7 @@
         <v>43705.83</v>
       </c>
       <c r="G133">
-        <v>12.9658</v>
+        <v>12.8705</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
@@ -4280,10 +4313,10 @@
         <v>135</v>
       </c>
       <c r="B134">
-        <v>87.662036490369005</v>
+        <v>87.009585611117004</v>
       </c>
       <c r="C134">
-        <v>88.040579502176001</v>
+        <v>88.040578573969</v>
       </c>
       <c r="D134">
         <v>41.613375849309001</v>
@@ -4295,7 +4328,7 @@
         <v>45278.06</v>
       </c>
       <c r="G134">
-        <v>12.7094</v>
+        <v>12.699</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.2">
@@ -4303,10 +4336,10 @@
         <v>136</v>
       </c>
       <c r="B135">
-        <v>85.139133974268006</v>
+        <v>85.419715570335995</v>
       </c>
       <c r="C135">
-        <v>78.031284717126994</v>
+        <v>78.031283838468994</v>
       </c>
       <c r="D135">
         <v>39.688212720411997</v>
@@ -4318,7 +4351,7 @@
         <v>44120.99</v>
       </c>
       <c r="G135">
-        <v>12.779500000000001</v>
+        <v>12.722899999999999</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.2">
@@ -4326,10 +4359,10 @@
         <v>137</v>
       </c>
       <c r="B136">
-        <v>87.348826065281003</v>
+        <v>89.895711426749003</v>
       </c>
       <c r="C136">
-        <v>68.609070955744997</v>
+        <v>68.609070249691996</v>
       </c>
       <c r="D136">
         <v>39.933931587186002</v>
@@ -4341,7 +4374,7 @@
         <v>44077.09</v>
       </c>
       <c r="G136">
-        <v>12.3612</v>
+        <v>12.524699999999999</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
@@ -4349,10 +4382,10 @@
         <v>138</v>
       </c>
       <c r="B137">
-        <v>90.458044093774006</v>
+        <v>88.192812110473994</v>
       </c>
       <c r="C137">
-        <v>86.083372084697999</v>
+        <v>86.083370962691006</v>
       </c>
       <c r="D137">
         <v>39.836111711187002</v>
@@ -4364,7 +4397,7 @@
         <v>42263.48</v>
       </c>
       <c r="G137">
-        <v>12.1456</v>
+        <v>12.205</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
@@ -4372,10 +4405,10 @@
         <v>139</v>
       </c>
       <c r="B138">
-        <v>91.668921836161999</v>
+        <v>91.050459842937997</v>
       </c>
       <c r="C138">
-        <v>95.898813367271998</v>
+        <v>95.898812149424003</v>
       </c>
       <c r="D138">
         <v>39.447116122771</v>
@@ -4387,7 +4420,7 @@
         <v>41588.32</v>
       </c>
       <c r="G138">
-        <v>12.8035</v>
+        <v>12.311500000000001</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
@@ -4395,10 +4428,10 @@
         <v>140</v>
       </c>
       <c r="B139">
-        <v>89.262238827106998</v>
+        <v>90.289493354827002</v>
       </c>
       <c r="C139">
-        <v>103.334935929012</v>
+        <v>103.334934835658</v>
       </c>
       <c r="D139">
         <v>38.770561839289002</v>
@@ -4410,7 +4443,7 @@
         <v>40623.300000000003</v>
       </c>
       <c r="G139">
-        <v>13.027900000000001</v>
+        <v>12.9596</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
@@ -4418,10 +4451,10 @@
         <v>141</v>
       </c>
       <c r="B140">
-        <v>91.106923770907997</v>
+        <v>90.498413460549997</v>
       </c>
       <c r="C140">
-        <v>94.065230896944996</v>
+        <v>94.065230339237999</v>
       </c>
       <c r="D140">
         <v>40.656212356296002</v>
@@ -4433,7 +4466,7 @@
         <v>40837.879999999997</v>
       </c>
       <c r="G140">
-        <v>12.846399999999999</v>
+        <v>12.7659</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
@@ -4441,10 +4474,10 @@
         <v>142</v>
       </c>
       <c r="B141">
-        <v>90.191413720808995</v>
+        <v>90.075342360017004</v>
       </c>
       <c r="C141">
-        <v>72.091576464122994</v>
+        <v>72.091576414859006</v>
       </c>
       <c r="D141">
         <v>40.530821931584001</v>
@@ -4456,7 +4489,7 @@
         <v>39492.370000000003</v>
       </c>
       <c r="G141">
-        <v>13.3415</v>
+        <v>12.9178</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
@@ -4464,10 +4497,10 @@
         <v>143</v>
       </c>
       <c r="B142">
-        <v>88.218546391496005</v>
+        <v>88.874458660924006</v>
       </c>
       <c r="C142">
-        <v>63.912108864800999</v>
+        <v>63.912109051239</v>
       </c>
       <c r="D142">
         <v>39.182486798399999</v>
@@ -4479,7 +4512,7 @@
         <v>40185.230000000003</v>
       </c>
       <c r="G142">
-        <v>13.1747</v>
+        <v>13.075900000000001</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
@@ -4487,10 +4520,10 @@
         <v>144</v>
       </c>
       <c r="B143">
-        <v>92.824761259767996</v>
+        <v>92.134160575300001</v>
       </c>
       <c r="C143">
-        <v>83.419765751857994</v>
+        <v>83.419766567495003</v>
       </c>
       <c r="D143">
         <v>38.077522808406997</v>
@@ -4502,7 +4535,7 @@
         <v>41038.65</v>
       </c>
       <c r="G143">
-        <v>13.0067</v>
+        <v>12.9992</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
@@ -4510,10 +4543,10 @@
         <v>145</v>
       </c>
       <c r="B144">
-        <v>93.048242861844997</v>
+        <v>93.054307040321007</v>
       </c>
       <c r="C144">
-        <v>108.935086173371</v>
+        <v>108.935088377635</v>
       </c>
       <c r="D144">
         <v>36.946459914668999</v>
@@ -4525,7 +4558,7 @@
         <v>42499.13</v>
       </c>
       <c r="G144">
-        <v>13.110099999999999</v>
+        <v>13.079599999999999</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.2">
@@ -4533,10 +4566,10 @@
         <v>146</v>
       </c>
       <c r="B145">
-        <v>92.094950630314997</v>
+        <v>92.400402119321001</v>
       </c>
       <c r="C145">
-        <v>111.054233623103</v>
+        <v>111.054236969862</v>
       </c>
       <c r="D145">
         <v>37.370687475109001</v>
@@ -4548,7 +4581,7 @@
         <v>42727.09</v>
       </c>
       <c r="G145">
-        <v>13.084300000000001</v>
+        <v>13.0076</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.2">
@@ -4556,10 +4589,10 @@
         <v>147</v>
       </c>
       <c r="B146">
-        <v>88.055324438121005</v>
+        <v>87.460845449060002</v>
       </c>
       <c r="C146">
-        <v>86.271807246397003</v>
+        <v>86.271810477605996</v>
       </c>
       <c r="D146">
         <v>35.55082196899</v>
@@ -4571,7 +4604,7 @@
         <v>40879.75</v>
       </c>
       <c r="G146">
-        <v>13.376899999999999</v>
+        <v>13.223000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.2">
@@ -4579,10 +4612,10 @@
         <v>148</v>
       </c>
       <c r="B147">
-        <v>86.924389672621004</v>
+        <v>87.210600972948995</v>
       </c>
       <c r="C147">
-        <v>85.741023024301001</v>
+        <v>85.741026876134001</v>
       </c>
       <c r="D147">
         <v>35.734569280526998</v>
@@ -4594,7 +4627,7 @@
         <v>38782.89</v>
       </c>
       <c r="G147">
-        <v>13.2379</v>
+        <v>13.280799999999999</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.2">
@@ -4602,10 +4635,10 @@
         <v>149</v>
       </c>
       <c r="B148">
-        <v>91.513084907484995</v>
+        <v>91.708777928421</v>
       </c>
       <c r="C148">
-        <v>73.373584263910004</v>
+        <v>73.373587210329006</v>
       </c>
       <c r="D148">
         <v>37.135146875798</v>
@@ -4617,7 +4650,7 @@
         <v>40461.599999999999</v>
       </c>
       <c r="G148">
-        <v>13.0549</v>
+        <v>13.1951</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.2">
@@ -4625,10 +4658,10 @@
         <v>150</v>
       </c>
       <c r="B149">
-        <v>90.606822317194002</v>
+        <v>90.843416601008997</v>
       </c>
       <c r="C149">
-        <v>87.090816088742997</v>
+        <v>87.090820249944002</v>
       </c>
       <c r="D149">
         <v>37.610133678604001</v>
@@ -4640,7 +4673,7 @@
         <v>40711.56</v>
       </c>
       <c r="G149">
-        <v>13.0901</v>
+        <v>13.0708</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.2">
@@ -4648,10 +4681,10 @@
         <v>151</v>
       </c>
       <c r="B150">
-        <v>93.771731551873003</v>
+        <v>93.651750216579998</v>
       </c>
       <c r="C150">
-        <v>101.638109685038</v>
+        <v>101.63811462724099</v>
       </c>
       <c r="D150">
         <v>37.751338610127</v>
@@ -4663,7 +4696,7 @@
         <v>41362.51</v>
       </c>
       <c r="G150">
-        <v>12.860900000000001</v>
+        <v>12.9247</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -4671,10 +4704,10 @@
         <v>152</v>
       </c>
       <c r="B151">
-        <v>92.240837913518007</v>
+        <v>92.926341732986003</v>
       </c>
       <c r="C151">
-        <v>102.898031910486</v>
+        <v>102.898035860615</v>
       </c>
       <c r="D151">
         <v>37.904949226010999</v>
@@ -4686,7 +4719,7 @@
         <v>42737.17</v>
       </c>
       <c r="G151">
-        <v>12.9712</v>
+        <v>12.995799999999999</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.2">
@@ -4694,10 +4727,10 @@
         <v>153</v>
       </c>
       <c r="B152">
-        <v>94.151086407885003</v>
+        <v>93.450291972260004</v>
       </c>
       <c r="C152">
-        <v>97.567371783216998</v>
+        <v>97.567373935098004</v>
       </c>
       <c r="D152">
         <v>37.551813280327003</v>
@@ -4709,7 +4742,7 @@
         <v>43817.69</v>
       </c>
       <c r="G152">
-        <v>13.226900000000001</v>
+        <v>12.990399999999999</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.2">
@@ -4717,10 +4750,10 @@
         <v>154</v>
       </c>
       <c r="B153">
-        <v>91.269250295223003</v>
+        <v>92.006983051806003</v>
       </c>
       <c r="C153">
-        <v>76.367087234055006</v>
+        <v>76.367087399913999</v>
       </c>
       <c r="D153">
         <v>37.450159922914999</v>
@@ -4732,7 +4765,7 @@
         <v>45628.09</v>
       </c>
       <c r="G153">
-        <v>13.0763</v>
+        <v>13.140599999999999</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.2">
@@ -4740,10 +4773,10 @@
         <v>155</v>
       </c>
       <c r="B154">
-        <v>91.305022134552004</v>
+        <v>90.879160878440999</v>
       </c>
       <c r="C154">
-        <v>67.752932796371994</v>
+        <v>67.752931922024004</v>
       </c>
       <c r="D154">
         <v>38.219888179972003</v>
@@ -4755,7 +4788,7 @@
         <v>44985.66</v>
       </c>
       <c r="G154">
-        <v>13.433</v>
+        <v>13.235200000000001</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.2">
@@ -4763,10 +4796,10 @@
         <v>156</v>
       </c>
       <c r="B155">
-        <v>95.618831810000998</v>
+        <v>94.973807063695006</v>
       </c>
       <c r="C155">
-        <v>80.235727415162998</v>
+        <v>80.235724512085</v>
       </c>
       <c r="D155">
         <v>37.693542023310002</v>
@@ -4778,7 +4811,7 @@
         <v>45027.519999999997</v>
       </c>
       <c r="G155">
-        <v>13.4773</v>
+        <v>13.4763</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.2">
@@ -4786,10 +4819,10 @@
         <v>157</v>
       </c>
       <c r="B156">
-        <v>94.901717686577996</v>
+        <v>95.994415298332996</v>
       </c>
       <c r="C156">
-        <v>110.506176726465</v>
+        <v>110.50616829773</v>
       </c>
       <c r="D156">
         <v>38.475968975641003</v>
@@ -4801,7 +4834,7 @@
         <v>44190.47</v>
       </c>
       <c r="G156">
-        <v>13.8965</v>
+        <v>13.621600000000001</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.2">
@@ -4809,10 +4842,10 @@
         <v>158</v>
       </c>
       <c r="B157">
-        <v>95.498426289845</v>
+        <v>94.860081976748006</v>
       </c>
       <c r="C157">
-        <v>116.221277101331</v>
+        <v>116.221263906758</v>
       </c>
       <c r="D157">
         <v>38.691437136761003</v>
@@ -4824,7 +4857,7 @@
         <v>43145.66</v>
       </c>
       <c r="G157">
-        <v>14.741400000000001</v>
+        <v>14.5129</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.2">
@@ -4832,10 +4865,10 @@
         <v>159</v>
       </c>
       <c r="B158">
-        <v>90.618368320502995</v>
+        <v>90.501794790833003</v>
       </c>
       <c r="C158">
-        <v>93.437850135386</v>
+        <v>93.437836777114001</v>
       </c>
       <c r="D158">
         <v>38.062504132065001</v>
@@ -4847,7 +4880,7 @@
         <v>40950.58</v>
       </c>
       <c r="G158">
-        <v>14.9885</v>
+        <v>14.692600000000001</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.2">
@@ -4855,10 +4888,10 @@
         <v>160</v>
       </c>
       <c r="B159">
-        <v>89.267735409303995</v>
+        <v>89.562329479236993</v>
       </c>
       <c r="C159">
-        <v>87.836427664781993</v>
+        <v>87.836413600038995</v>
       </c>
       <c r="D159">
         <v>37.491142610506998</v>
@@ -4870,7 +4903,7 @@
         <v>44190.17</v>
       </c>
       <c r="G159">
-        <v>14.955299999999999</v>
+        <v>14.9213</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.2">
@@ -4878,10 +4911,10 @@
         <v>161</v>
       </c>
       <c r="B160">
-        <v>94.331541870421006</v>
+        <v>93.822626332976995</v>
       </c>
       <c r="C160">
-        <v>76.092626742289994</v>
+        <v>76.092615862748005</v>
       </c>
       <c r="D160">
         <v>38.505218872516998</v>
@@ -4893,7 +4926,7 @@
         <v>43724.78</v>
       </c>
       <c r="G160">
-        <v>15.264699999999999</v>
+        <v>15.228300000000001</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.2">
@@ -4901,10 +4934,10 @@
         <v>162</v>
       </c>
       <c r="B161">
-        <v>92.929379446205004</v>
+        <v>93.427189325648996</v>
       </c>
       <c r="C161">
-        <v>87.801227389530993</v>
+        <v>87.801213247145995</v>
       </c>
       <c r="D161">
         <v>37.842864420837998</v>
@@ -4916,7 +4949,7 @@
         <v>44582.39</v>
       </c>
       <c r="G161">
-        <v>15.3714</v>
+        <v>15.2262</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.2">
@@ -4924,10 +4957,10 @@
         <v>163</v>
       </c>
       <c r="B162">
-        <v>94.018450628531994</v>
+        <v>94.778210921173994</v>
       </c>
       <c r="C162">
-        <v>102.836206598768</v>
+        <v>102.836189778639</v>
       </c>
       <c r="D162">
         <v>38.031691558285999</v>
@@ -4939,7 +4972,7 @@
         <v>44703.62</v>
       </c>
       <c r="G162">
-        <v>15.381500000000001</v>
+        <v>15.2645</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.2">
@@ -4947,10 +4980,10 @@
         <v>164</v>
       </c>
       <c r="B163">
-        <v>95.598730186151002</v>
+        <v>95.153134010382999</v>
       </c>
       <c r="C163">
-        <v>98.480766886672001</v>
+        <v>98.480754731473994</v>
       </c>
       <c r="D163">
         <v>39.111922237709003</v>
@@ -4962,7 +4995,7 @@
         <v>45053.7</v>
       </c>
       <c r="G163">
-        <v>15.6854</v>
+        <v>15.483000000000001</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.2">
@@ -4970,10 +5003,10 @@
         <v>165</v>
       </c>
       <c r="B164">
-        <v>96.244186709492993</v>
+        <v>95.594589851790005</v>
       </c>
       <c r="C164">
-        <v>91.336649305509994</v>
+        <v>91.336643036238996</v>
       </c>
       <c r="D164">
         <v>38.131884189947002</v>
@@ -4985,7 +5018,7 @@
         <v>44752.93</v>
       </c>
       <c r="G164">
-        <v>16.077200000000001</v>
+        <v>15.9396</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -4993,10 +5026,10 @@
         <v>166</v>
       </c>
       <c r="B165">
-        <v>93.906884866571005</v>
+        <v>94.932593495885996</v>
       </c>
       <c r="C165">
-        <v>75.706359928365998</v>
+        <v>75.706359167048006</v>
       </c>
       <c r="D165">
         <v>37.383557196311997</v>
@@ -5008,7 +5041,7 @@
         <v>43721.96</v>
       </c>
       <c r="G165">
-        <v>16.782900000000001</v>
+        <v>16.536799999999999</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.2">
@@ -5016,10 +5049,10 @@
         <v>167</v>
       </c>
       <c r="B166">
-        <v>95.487849559279994</v>
+        <v>94.905469065353998</v>
       </c>
       <c r="C166">
-        <v>69.968934544064993</v>
+        <v>69.968937148975002</v>
       </c>
       <c r="D166">
         <v>37.449011862978999</v>
@@ -5031,7 +5064,7 @@
         <v>42632.54</v>
       </c>
       <c r="G166">
-        <v>16.9053</v>
+        <v>16.857800000000001</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.2">
@@ -5039,10 +5072,10 @@
         <v>168</v>
       </c>
       <c r="B167">
-        <v>97.291796805640004</v>
+        <v>97.167236297311007</v>
       </c>
       <c r="C167">
-        <v>80.927279933644002</v>
+        <v>80.927288838755999</v>
       </c>
       <c r="D167">
         <v>37.813079113192003</v>
@@ -5054,7 +5087,7 @@
         <v>44542.76</v>
       </c>
       <c r="G167">
-        <v>16.5244</v>
+        <v>16.564</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.2">
@@ -5062,10 +5095,10 @@
         <v>169</v>
       </c>
       <c r="B168">
-        <v>96.719780210416005</v>
+        <v>97.438620270968997</v>
       </c>
       <c r="C168">
-        <v>109.881289865111</v>
+        <v>109.88131685600899</v>
       </c>
       <c r="D168">
         <v>38.182935259201997</v>
@@ -5077,7 +5110,7 @@
         <v>43418.55</v>
       </c>
       <c r="G168">
-        <v>16.585599999999999</v>
+        <v>16.6357</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.2">
@@ -5085,10 +5118,10 @@
         <v>170</v>
       </c>
       <c r="B169">
-        <v>97.507999245090005</v>
+        <v>96.782307884475003</v>
       </c>
       <c r="C169">
-        <v>127.128307066996</v>
+        <v>127.12835701693599</v>
       </c>
       <c r="D169">
         <v>38.368540211141998</v>
@@ -5100,7 +5133,7 @@
         <v>42977.5</v>
       </c>
       <c r="G169">
-        <v>17.248699999999999</v>
+        <v>17.066600000000001</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.2">
@@ -5108,10 +5141,10 @@
         <v>171</v>
       </c>
       <c r="B170">
-        <v>91.735212811975998</v>
+        <v>92.476751035481996</v>
       </c>
       <c r="C170">
-        <v>97.767299096122997</v>
+        <v>97.767347056768003</v>
       </c>
       <c r="D170">
         <v>38.181521075725001</v>
@@ -5123,7 +5156,7 @@
         <v>43630.77</v>
       </c>
       <c r="G170">
-        <v>18.1935</v>
+        <v>18.072800000000001</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.2">
@@ -5131,10 +5164,10 @@
         <v>172</v>
       </c>
       <c r="B171">
-        <v>92.725315287884996</v>
+        <v>91.760313798468005</v>
       </c>
       <c r="C171">
-        <v>87.310864004273995</v>
+        <v>87.310910690631999</v>
       </c>
       <c r="D171">
         <v>36.732083562291997</v>
@@ -5146,7 +5179,7 @@
         <v>43714.93</v>
       </c>
       <c r="G171">
-        <v>18.102</v>
+        <v>18.473099999999999</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.2">
@@ -5154,10 +5187,10 @@
         <v>173</v>
       </c>
       <c r="B172">
-        <v>94.127303896792995</v>
+        <v>95.379157273581995</v>
       </c>
       <c r="C172">
-        <v>69.883284512187998</v>
+        <v>69.883314992573005</v>
       </c>
       <c r="D172">
         <v>36.814432418720997</v>
@@ -5169,7 +5202,7 @@
         <v>45881.08</v>
       </c>
       <c r="G172">
-        <v>17.236999999999998</v>
+        <v>17.649000000000001</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.2">
@@ -5177,10 +5210,10 @@
         <v>174</v>
       </c>
       <c r="B173">
-        <v>95.749506219249</v>
+        <v>93.795098817427998</v>
       </c>
       <c r="C173">
-        <v>90.418275355144004</v>
+        <v>90.418328223393004</v>
       </c>
       <c r="D173">
         <v>36.713858243741001</v>
@@ -5192,7 +5225,7 @@
         <v>45784.77</v>
       </c>
       <c r="G173">
-        <v>17.1767</v>
+        <v>17.4877</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.2">
@@ -5200,10 +5233,10 @@
         <v>175</v>
       </c>
       <c r="B174">
-        <v>96.000095211526002</v>
+        <v>96.318351739560001</v>
       </c>
       <c r="C174">
-        <v>97.270740993478995</v>
+        <v>97.270796581135002</v>
       </c>
       <c r="D174">
         <v>37.484803883049999</v>
@@ -5215,7 +5248,7 @@
         <v>45459.45</v>
       </c>
       <c r="G174">
-        <v>18.411799999999999</v>
+        <v>18.154199999999999</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.2">
@@ -5223,10 +5256,10 @@
         <v>176</v>
       </c>
       <c r="B175">
-        <v>97.383344358074993</v>
+        <v>97.054550766473</v>
       </c>
       <c r="C175">
-        <v>108.831494329124</v>
+        <v>108.831549143098</v>
       </c>
       <c r="D175">
         <v>38.349095003102001</v>
@@ -5238,7 +5271,7 @@
         <v>45966.49</v>
       </c>
       <c r="G175">
-        <v>18.464600000000001</v>
+        <v>18.652999999999999</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.2">
@@ -5246,10 +5279,10 @@
         <v>177</v>
       </c>
       <c r="B176">
-        <v>95.394397799594003</v>
+        <v>96.165336984560994</v>
       </c>
       <c r="C176">
-        <v>92.78609189334</v>
+        <v>92.786117915671994</v>
       </c>
       <c r="D176">
         <v>36.506041112359</v>
@@ -5261,7 +5294,7 @@
         <v>46660.67</v>
       </c>
       <c r="G176">
-        <v>18.7837</v>
+        <v>18.601400000000002</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.2">
@@ -5269,10 +5302,10 @@
         <v>178</v>
       </c>
       <c r="B177">
-        <v>96.882042007883001</v>
+        <v>96.234836981626003</v>
       </c>
       <c r="C177">
-        <v>87.061221361787005</v>
+        <v>87.061228182904998</v>
       </c>
       <c r="D177">
         <v>35.655436898837998</v>
@@ -5284,7 +5317,7 @@
         <v>47541.32</v>
       </c>
       <c r="G177">
-        <v>18.8611</v>
+        <v>18.474900000000002</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.2">
@@ -5292,10 +5325,10 @@
         <v>179</v>
       </c>
       <c r="B178">
-        <v>95.737167365266998</v>
+        <v>95.284002624779006</v>
       </c>
       <c r="C178">
-        <v>72.483314939745</v>
+        <v>72.483306639930007</v>
       </c>
       <c r="D178">
         <v>34.754994253749999</v>
@@ -5307,7 +5340,7 @@
         <v>47245.8</v>
       </c>
       <c r="G178">
-        <v>19.377600000000001</v>
+        <v>19.192399999999999</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.2">
@@ -5315,10 +5348,10 @@
         <v>180</v>
       </c>
       <c r="B179">
-        <v>97.662658168115001</v>
+        <v>98.729614177735996</v>
       </c>
       <c r="C179">
-        <v>84.298048956819002</v>
+        <v>84.298016772268994</v>
       </c>
       <c r="D179">
         <v>35.031896434495003</v>
@@ -5330,7 +5363,7 @@
         <v>48009.279999999999</v>
       </c>
       <c r="G179">
-        <v>18.8887</v>
+        <v>18.892399999999999</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -5338,10 +5371,10 @@
         <v>181</v>
       </c>
       <c r="B180">
-        <v>100.849512430011</v>
+        <v>100.234757825496</v>
       </c>
       <c r="C180">
-        <v>116.775678738176</v>
+        <v>116.77557491341901</v>
       </c>
       <c r="D180">
         <v>34.875177957368003</v>
@@ -5350,10 +5383,10 @@
         <v>43.689080044792</v>
       </c>
       <c r="F180">
-        <v>45285.5</v>
+        <v>45315.96</v>
       </c>
       <c r="G180">
-        <v>20.515499999999999</v>
+        <v>20.118500000000001</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -5361,10 +5394,10 @@
         <v>182</v>
       </c>
       <c r="B181">
-        <v>99.785591288738004</v>
+        <v>99.658038082920001</v>
       </c>
       <c r="C181">
-        <v>127.895401833675</v>
+        <v>127.89522490207899</v>
       </c>
       <c r="D181">
         <v>35.478418724981999</v>
@@ -5376,7 +5409,7 @@
         <v>45642.9</v>
       </c>
       <c r="G181">
-        <v>20.619399999999999</v>
+        <v>20.520600000000002</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5384,10 +5417,10 @@
         <v>183</v>
       </c>
       <c r="B182">
-        <v>95.147313888778001</v>
+        <v>95.462523051706995</v>
       </c>
       <c r="C182">
-        <v>110.50326505917801</v>
+        <v>110.50305541117299</v>
       </c>
       <c r="D182">
         <v>28.667872479598</v>
@@ -5399,7 +5432,7 @@
         <v>47001.06</v>
       </c>
       <c r="G182">
-        <v>20.790800000000001</v>
+        <v>21.385300000000001</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
@@ -5407,10 +5440,10 @@
         <v>184</v>
       </c>
       <c r="B183">
-        <v>93.328137359669995</v>
+        <v>93.635715885180005</v>
       </c>
       <c r="C183">
-        <v>84.592400142404003</v>
+        <v>84.592251096968994</v>
       </c>
       <c r="D183">
         <v>31.515609602348999</v>
@@ -5422,7 +5455,7 @@
         <v>46856.79</v>
       </c>
       <c r="G183">
-        <v>19.995699999999999</v>
+        <v>20.290500000000002</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
@@ -5430,10 +5463,10 @@
         <v>185</v>
       </c>
       <c r="B184">
-        <v>99.882180876967993</v>
+        <v>98.346206852098007</v>
       </c>
       <c r="C184">
-        <v>74.490048242349005</v>
+        <v>74.489928901479999</v>
       </c>
       <c r="D184">
         <v>33.795125366694997</v>
@@ -5445,7 +5478,7 @@
         <v>48541.56</v>
       </c>
       <c r="G184">
-        <v>18.795500000000001</v>
+        <v>19.300999999999998</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -5453,10 +5486,10 @@
         <v>186</v>
       </c>
       <c r="B185">
-        <v>94.250918428263006</v>
+        <v>96.171377125768004</v>
       </c>
       <c r="C185">
-        <v>91.616791984301003</v>
+        <v>91.616610057120994</v>
       </c>
       <c r="D185">
         <v>34.934500730947001</v>
@@ -5468,7 +5501,7 @@
         <v>49261.33</v>
       </c>
       <c r="G185">
-        <v>18.959399999999999</v>
+        <v>18.787500000000001</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.2">
@@ -5476,10 +5509,10 @@
         <v>187</v>
       </c>
       <c r="B186">
-        <v>99.160532458662999</v>
+        <v>98.498613467259005</v>
       </c>
       <c r="C186">
-        <v>98.554199782904007</v>
+        <v>98.55401035621</v>
       </c>
       <c r="D186">
         <v>35.873278680958002</v>
@@ -5491,7 +5524,7 @@
         <v>48788.44</v>
       </c>
       <c r="G186">
-        <v>18.690899999999999</v>
+        <v>18.755700000000001</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.2">
@@ -5499,10 +5532,10 @@
         <v>188</v>
       </c>
       <c r="B187">
-        <v>99.894631597867999</v>
+        <v>99.422328276447999</v>
       </c>
       <c r="C187">
-        <v>114.404124071635</v>
+        <v>114.40392708925501</v>
       </c>
       <c r="D187">
         <v>36.010357040914002</v>
@@ -5514,7 +5547,7 @@
         <v>49857.49</v>
       </c>
       <c r="G187">
-        <v>18.0626</v>
+        <v>18.1326</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.2">
@@ -5522,10 +5555,10 @@
         <v>189</v>
       </c>
       <c r="B188">
-        <v>96.513983795048006</v>
+        <v>97.568065518672</v>
       </c>
       <c r="C188">
-        <v>96.553851536172999</v>
+        <v>96.553762545645995</v>
       </c>
       <c r="D188">
         <v>36.488627292064997</v>
@@ -5537,7 +5570,7 @@
         <v>51011.87</v>
       </c>
       <c r="G188">
-        <v>17.864599999999999</v>
+        <v>17.828299999999999</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
@@ -5545,10 +5578,10 @@
         <v>190</v>
       </c>
       <c r="B189">
-        <v>99.228384165080996</v>
+        <v>98.489506981587994</v>
       </c>
       <c r="C189">
-        <v>81.902714241908001</v>
+        <v>81.902698902807003</v>
       </c>
       <c r="D189">
         <v>36.505500828123999</v>
@@ -5560,7 +5593,7 @@
         <v>51210.48</v>
       </c>
       <c r="G189">
-        <v>17.814499999999999</v>
+        <v>17.806999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
@@ -5568,10 +5601,10 @@
         <v>191</v>
       </c>
       <c r="B190">
-        <v>95.757537186538002</v>
+        <v>95.763490663528003</v>
       </c>
       <c r="C190">
-        <v>73.895489204124999</v>
+        <v>73.895519100160001</v>
       </c>
       <c r="D190">
         <v>36.787947686430002</v>
@@ -5583,7 +5616,7 @@
         <v>50346.06</v>
       </c>
       <c r="G190">
-        <v>18.158999999999999</v>
+        <v>17.835699999999999</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
@@ -5591,10 +5624,10 @@
         <v>192</v>
       </c>
       <c r="B191">
-        <v>99.456509210622997</v>
+        <v>99.785812402184007</v>
       </c>
       <c r="C191">
-        <v>85.902924568407997</v>
+        <v>85.903037986756004</v>
       </c>
       <c r="D191">
         <v>36.436983240153999</v>
@@ -5606,7 +5639,7 @@
         <v>48625.53</v>
       </c>
       <c r="G191">
-        <v>19.1478</v>
+        <v>18.816099999999999</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
@@ -5614,10 +5647,10 @@
         <v>193</v>
       </c>
       <c r="B192">
-        <v>102.799035518046</v>
+        <v>102.452283912415</v>
       </c>
       <c r="C192">
-        <v>129.32101715020201</v>
+        <v>129.321428901205</v>
       </c>
       <c r="D192">
         <v>36.716793474580001</v>
@@ -5629,7 +5662,7 @@
         <v>47092.44</v>
       </c>
       <c r="G192">
-        <v>18.622900000000001</v>
+        <v>18.915800000000001</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.2">
@@ -5637,10 +5670,10 @@
         <v>194</v>
       </c>
       <c r="B193">
-        <v>100.82449289261299</v>
+        <v>101.63924288877099</v>
       </c>
       <c r="C193">
-        <v>128.46494304206001</v>
+        <v>128.465538676867</v>
       </c>
       <c r="D193">
         <v>36.315462765375997</v>
@@ -5652,7 +5685,7 @@
         <v>49354.42</v>
       </c>
       <c r="G193">
-        <v>19.6629</v>
+        <v>19.1812</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.2">
@@ -5660,10 +5693,10 @@
         <v>195</v>
       </c>
       <c r="B194">
-        <v>97.406006083587002</v>
+        <v>96.755336708906</v>
       </c>
       <c r="C194">
-        <v>112.03419373166901</v>
+        <v>112.03490349711301</v>
       </c>
       <c r="D194">
         <v>34.801847205944</v>
@@ -5675,7 +5708,7 @@
         <v>50456.17</v>
       </c>
       <c r="G194">
-        <v>18.6069</v>
+        <v>18.907399999999999</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.2">
@@ -5683,10 +5716,10 @@
         <v>196</v>
       </c>
       <c r="B195">
-        <v>95.319076819998003</v>
+        <v>95.633280499522996</v>
       </c>
       <c r="C195">
-        <v>92.131257013679999</v>
+        <v>92.131830660770007</v>
       </c>
       <c r="D195">
         <v>34.189339177953002</v>
@@ -5698,7 +5731,7 @@
         <v>47437.93</v>
       </c>
       <c r="G195">
-        <v>18.833100000000002</v>
+        <v>18.6449</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.2">
@@ -5706,10 +5739,10 @@
         <v>197</v>
       </c>
       <c r="B196">
-        <v>98.984067330138998</v>
+        <v>100.923256947146</v>
       </c>
       <c r="C196">
-        <v>77.898360711544996</v>
+        <v>77.898779452189004</v>
       </c>
       <c r="D196">
         <v>34.336726438239999</v>
@@ -5721,7 +5754,7 @@
         <v>46124.85</v>
       </c>
       <c r="G196">
-        <v>18.270900000000001</v>
+        <v>18.630800000000001</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.2">
@@ -5729,10 +5762,10 @@
         <v>198</v>
       </c>
       <c r="B197">
-        <v>98.915163384148002</v>
+        <v>97.609807201197</v>
       </c>
       <c r="C197">
-        <v>96.619390394384993</v>
+        <v>96.620041235241004</v>
       </c>
       <c r="D197">
         <v>35.611584664380999</v>
@@ -5744,7 +5777,7 @@
         <v>48358.16</v>
       </c>
       <c r="G197">
-        <v>18.787800000000001</v>
+        <v>18.3872</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.2">
@@ -5752,10 +5785,10 @@
         <v>199</v>
       </c>
       <c r="B198">
-        <v>102.01300513439401</v>
+        <v>101.25377993825001</v>
       </c>
       <c r="C198">
-        <v>108.578590197669</v>
+        <v>108.579313047244</v>
       </c>
       <c r="D198">
         <v>36.647874828558997</v>
@@ -5767,7 +5800,7 @@
         <v>44662.55</v>
       </c>
       <c r="G198">
-        <v>19.975899999999999</v>
+        <v>19.591000000000001</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.2">
@@ -5775,10 +5808,10 @@
         <v>202</v>
       </c>
       <c r="B199">
-        <v>101.245824386902</v>
+        <v>101.251862654729</v>
       </c>
       <c r="C199">
-        <v>111.26239131655799</v>
+        <v>111.26298448631201</v>
       </c>
       <c r="D199">
         <v>37.148299568801001</v>
@@ -5790,7 +5823,7 @@
         <v>47663.199999999997</v>
       </c>
       <c r="G199">
-        <v>19.691199999999998</v>
+        <v>20.3032</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.2">
@@ -5798,10 +5831,10 @@
         <v>203</v>
       </c>
       <c r="B200">
-        <v>100.145973924199</v>
+        <v>100.478100555312</v>
       </c>
       <c r="C200">
-        <v>98.316286838398</v>
+        <v>98.316561439479997</v>
       </c>
       <c r="D200">
         <v>43.341085684473001</v>
@@ -5813,7 +5846,7 @@
         <v>49698.01</v>
       </c>
       <c r="G200">
-        <v>18.645700000000001</v>
+        <v>19.009499999999999</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.2">
@@ -5821,10 +5854,10 @@
         <v>204</v>
       </c>
       <c r="B201">
-        <v>101.605932756206</v>
+        <v>100.92040954741</v>
       </c>
       <c r="C201">
-        <v>81.073402626952998</v>
+        <v>81.073429683369994</v>
       </c>
       <c r="D201">
         <v>43.005686306386998</v>
@@ -5836,7 +5869,7 @@
         <v>49547.68</v>
       </c>
       <c r="G201">
-        <v>19.179200000000002</v>
+        <v>18.857500000000002</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.2">
@@ -5844,10 +5877,10 @@
         <v>205</v>
       </c>
       <c r="B202">
-        <v>97.997563463334998</v>
+        <v>99.126053301363001</v>
       </c>
       <c r="C202">
-        <v>73.663477863319002</v>
+        <v>73.663376670377005</v>
       </c>
       <c r="D202">
         <v>42.132704095465002</v>
@@ -5859,7 +5892,7 @@
         <v>49504.160000000003</v>
       </c>
       <c r="G202">
-        <v>18.723099999999999</v>
+        <v>19.0154</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.2">
@@ -5867,10 +5900,10 @@
         <v>206</v>
       </c>
       <c r="B203">
-        <v>102.342026751601</v>
+        <v>101.65935799437</v>
       </c>
       <c r="C203">
-        <v>82.241053719714998</v>
+        <v>82.240723018249</v>
       </c>
       <c r="D203">
         <v>42.533012467452998</v>
@@ -5882,7 +5915,7 @@
         <v>43942.55</v>
       </c>
       <c r="G203">
-        <v>20.317699999999999</v>
+        <v>19.1859</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.2">
@@ -5890,10 +5923,10 @@
         <v>207</v>
       </c>
       <c r="B204">
-        <v>104.00535486155</v>
+        <v>103.513876317335</v>
       </c>
       <c r="C204">
-        <v>131.74842310561101</v>
+        <v>131.74700679574801</v>
       </c>
       <c r="D204">
         <v>41.675040786563997</v>
@@ -5905,7 +5938,7 @@
         <v>41732.78</v>
       </c>
       <c r="G204">
-        <v>20.345500000000001</v>
+        <v>20.261199999999999</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.2">
@@ -5913,10 +5946,10 @@
         <v>208</v>
       </c>
       <c r="B205">
-        <v>100.020005103937</v>
+        <v>101.113366778323</v>
       </c>
       <c r="C205">
-        <v>134.43317248044499</v>
+        <v>134.431050013852</v>
       </c>
       <c r="D205">
         <v>44.865438497928999</v>
@@ -5928,7 +5961,7 @@
         <v>41640.269999999997</v>
       </c>
       <c r="G205">
-        <v>19.651199999999999</v>
+        <v>20.1112</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.2">
@@ -5936,10 +5969,10 @@
         <v>209</v>
       </c>
       <c r="B206">
-        <v>98.523257711729997</v>
+        <v>97.791738978523</v>
       </c>
       <c r="C206">
-        <v>112.527547148605</v>
+        <v>112.525191647136</v>
       </c>
       <c r="D206">
         <v>45.929883044867999</v>
@@ -5951,7 +5984,7 @@
         <v>43987.94</v>
       </c>
       <c r="G206">
-        <v>19.038799999999998</v>
+        <v>19.165099999999999</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.2">
@@ -5959,10 +5992,10 @@
         <v>210</v>
       </c>
       <c r="B207">
-        <v>95.934467005502995</v>
+        <v>96.252314837569003</v>
       </c>
       <c r="C207">
-        <v>97.184841796978006</v>
+        <v>97.18277765162</v>
       </c>
       <c r="D207">
         <v>47.826149713221</v>
@@ -5974,7 +6007,7 @@
         <v>42823.81</v>
       </c>
       <c r="G207">
-        <v>19.2607</v>
+        <v>19.204899999999999</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.2">
@@ -5982,10 +6015,10 @@
         <v>211</v>
       </c>
       <c r="B208">
-        <v>99.928108122549006</v>
+        <v>99.862887629317001</v>
       </c>
       <c r="C208">
-        <v>79.542133835531004</v>
+        <v>79.540766556807</v>
       </c>
       <c r="D208">
         <v>46.341067759577001</v>
@@ -5997,7 +6030,7 @@
         <v>43281.279999999999</v>
       </c>
       <c r="G208">
-        <v>19.3779</v>
+        <v>19.247699999999998</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -6005,10 +6038,10 @@
         <v>212</v>
       </c>
       <c r="B209">
-        <v>97.673834858590993</v>
+        <v>98.072417153759005</v>
       </c>
       <c r="C209">
-        <v>94.072427545359005</v>
+        <v>94.070460720228994</v>
       </c>
       <c r="D209">
         <v>45.484973893286003</v>
@@ -6020,7 +6053,7 @@
         <v>44597.32</v>
       </c>
       <c r="G209">
-        <v>19.009899999999998</v>
+        <v>18.9864</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.2">
@@ -6028,10 +6061,10 @@
         <v>213</v>
       </c>
       <c r="B210">
-        <v>101.33425344825601</v>
+        <v>100.652231382953</v>
       </c>
       <c r="C210">
-        <v>108.366849864374</v>
+        <v>108.36454313495901</v>
       </c>
       <c r="D210">
         <v>44.323546935750997</v>
@@ -6043,7 +6076,7 @@
         <v>42749.16</v>
       </c>
       <c r="G210">
-        <v>19.642600000000002</v>
+        <v>19.119700000000002</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.2">
@@ -6051,10 +6084,10 @@
         <v>214</v>
       </c>
       <c r="B211">
-        <v>99.864756496479998</v>
+        <v>101.01555581740401</v>
       </c>
       <c r="C211">
-        <v>112.99362693834399</v>
+        <v>112.991693990751</v>
       </c>
       <c r="D211">
         <v>43.665842320727997</v>
@@ -6066,7 +6099,7 @@
         <v>43161.17</v>
       </c>
       <c r="G211">
-        <v>19.2087</v>
+        <v>19.2745</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.2">
@@ -6074,10 +6107,10 @@
         <v>215</v>
       </c>
       <c r="B212">
-        <v>100.508399218752</v>
+        <v>99.837608948888999</v>
       </c>
       <c r="C212">
-        <v>100.881474978593</v>
+        <v>100.880582154088</v>
       </c>
       <c r="D212">
         <v>43.317695798679999</v>
@@ -6089,7 +6122,7 @@
         <v>40863.089999999997</v>
       </c>
       <c r="G212">
-        <v>18.992899999999999</v>
+        <v>19.0534</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.2">
@@ -6097,10 +6130,10 @@
         <v>216</v>
       </c>
       <c r="B213">
-        <v>100.13507123274201</v>
+        <v>100.006590538084</v>
       </c>
       <c r="C213">
-        <v>79.071855135866997</v>
+        <v>79.071809972566001</v>
       </c>
       <c r="D213">
         <v>43.819211712737001</v>
@@ -6112,7 +6145,7 @@
         <v>42622.5</v>
       </c>
       <c r="G213">
-        <v>20.069600000000001</v>
+        <v>19.684999999999999</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.2">
@@ -6120,10 +6153,10 @@
         <v>217</v>
       </c>
       <c r="B214">
-        <v>97.493432242661001</v>
+        <v>98.217363586410002</v>
       </c>
       <c r="C214">
-        <v>78.247983835664002</v>
+        <v>78.248397684097</v>
       </c>
       <c r="D214">
         <v>45.299473488517002</v>
@@ -6135,7 +6168,7 @@
         <v>43011.27</v>
       </c>
       <c r="G214">
-        <v>19.734500000000001</v>
+        <v>19.586500000000001</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.2">
@@ -6143,10 +6176,10 @@
         <v>218</v>
       </c>
       <c r="B215">
-        <v>100.54338915205599</v>
+        <v>99.792735129557997</v>
       </c>
       <c r="C215">
-        <v>87.113290668548998</v>
+        <v>87.114543896168996</v>
       </c>
       <c r="D215">
         <v>44.059735903125997</v>
@@ -6158,7 +6191,7 @@
         <v>43337.279999999999</v>
       </c>
       <c r="G215">
-        <v>19.194800000000001</v>
+        <v>19.324200000000001</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.2">
@@ -6166,10 +6199,10 @@
         <v>219</v>
       </c>
       <c r="B216">
-        <v>102.89806536303399</v>
+        <v>102.901974496107</v>
       </c>
       <c r="C216">
-        <v>127.430429537373</v>
+        <v>127.43498099595899</v>
       </c>
       <c r="D216">
         <v>43.840726940102002</v>
@@ -6181,7 +6214,7 @@
         <v>42820.18</v>
       </c>
       <c r="G216">
-        <v>19.5352</v>
+        <v>19.3325</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.2">
@@ -6189,10 +6222,10 @@
         <v>220</v>
       </c>
       <c r="B217">
-        <v>99.936524009500005</v>
+        <v>100.263390896226</v>
       </c>
       <c r="C217">
-        <v>129.13346236020899</v>
+        <v>129.14017524106299</v>
       </c>
       <c r="D217">
         <v>43.757350301180999</v>
@@ -6204,7 +6237,7 @@
         <v>43541.02</v>
       </c>
       <c r="G217">
-        <v>18.8642</v>
+        <v>19.107099999999999</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.2">
@@ -6212,10 +6245,10 @@
         <v>221</v>
       </c>
       <c r="B218">
-        <v>98.312220036338999</v>
+        <v>97.643669678731996</v>
       </c>
       <c r="C218">
-        <v>112.588524155839</v>
+        <v>112.596440610782</v>
       </c>
       <c r="D218">
         <v>44.120454102384997</v>
@@ -6227,7 +6260,7 @@
         <v>44108.31</v>
       </c>
       <c r="G218">
-        <v>18.908200000000001</v>
+        <v>18.803999999999998</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.2">
@@ -6235,10 +6268,10 @@
         <v>222</v>
       </c>
       <c r="B219">
-        <v>95.265917571586996</v>
+        <v>94.649828409820003</v>
       </c>
       <c r="C219">
-        <v>86.719685982344004</v>
+        <v>86.724916097144003</v>
       </c>
       <c r="D219">
         <v>43.329942793901999</v>
@@ -6250,7 +6283,7 @@
         <v>41324.31</v>
       </c>
       <c r="G219">
-        <v>19.776</v>
+        <v>18.8443</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.2">
@@ -6258,10 +6291,10 @@
         <v>223</v>
       </c>
       <c r="B220">
-        <v>96.930291025206003</v>
+        <v>96.399635458499006</v>
       </c>
       <c r="C220">
-        <v>85.087556527744994</v>
+        <v>85.092803642912997</v>
       </c>
       <c r="D220">
         <v>42.059280695535001</v>
@@ -6273,7 +6306,7 @@
         <v>34554.53</v>
       </c>
       <c r="G220">
-        <v>23.4847</v>
+        <v>22.378399999999999</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.2">
@@ -6281,10 +6314,10 @@
         <v>224</v>
       </c>
       <c r="B221">
-        <v>76.335282413236001</v>
+        <v>76.741213352187003</v>
       </c>
       <c r="C221">
-        <v>93.769026708439995</v>
+        <v>93.775509425308996</v>
       </c>
       <c r="D221">
         <v>32.223545786244998</v>
@@ -6296,7 +6329,7 @@
         <v>36470.11</v>
       </c>
       <c r="G221">
-        <v>23.9283</v>
+        <v>24.265799999999999</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.2">
@@ -6304,10 +6337,10 @@
         <v>225</v>
       </c>
       <c r="B222">
-        <v>76.905359549721993</v>
+        <v>77.523814336192004</v>
       </c>
       <c r="C222">
-        <v>109.19370927600001</v>
+        <v>109.201580041369</v>
       </c>
       <c r="D222">
         <v>31.068243908700001</v>
@@ -6319,7 +6352,7 @@
         <v>36122.730000000003</v>
       </c>
       <c r="G222">
-        <v>22.177800000000001</v>
+        <v>23.422999999999998</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.2">
@@ -6327,10 +6360,10 @@
         <v>226</v>
       </c>
       <c r="B223">
-        <v>86.484866519304006</v>
+        <v>86.078654959632999</v>
       </c>
       <c r="C223">
-        <v>109.65199422633</v>
+        <v>109.658211714017</v>
       </c>
       <c r="D223">
         <v>31.957181906052998</v>
@@ -6342,7 +6375,7 @@
         <v>37716.43</v>
       </c>
       <c r="G223">
-        <v>23.089300000000001</v>
+        <v>22.298999999999999</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.2">
@@ -6350,10 +6383,10 @@
         <v>227</v>
       </c>
       <c r="B224">
-        <v>90.458169719512</v>
+        <v>89.845644607804005</v>
       </c>
       <c r="C224">
-        <v>109.444474687382</v>
+        <v>109.448097576702</v>
       </c>
       <c r="D224">
         <v>34.417344488575999</v>
@@ -6365,7 +6398,7 @@
         <v>37019.68</v>
       </c>
       <c r="G224">
-        <v>22.2012</v>
+        <v>22.403300000000002</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.2">
@@ -6373,10 +6406,10 @@
         <v>228</v>
       </c>
       <c r="B225">
-        <v>91.531600398435003</v>
+        <v>92.530644310561996</v>
       </c>
       <c r="C225">
-        <v>81.333500610848006</v>
+        <v>81.333755275345993</v>
       </c>
       <c r="D225">
         <v>35.064783138979998</v>
@@ -6388,7 +6421,7 @@
         <v>36840.730000000003</v>
       </c>
       <c r="G225">
-        <v>21.888000000000002</v>
+        <v>22.2072</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.2">
@@ -6396,10 +6429,10 @@
         <v>229</v>
       </c>
       <c r="B226">
-        <v>92.964074563563997</v>
+        <v>92.398854695142006</v>
       </c>
       <c r="C226">
-        <v>82.231147970913995</v>
+        <v>82.229805248402002</v>
       </c>
       <c r="D226">
         <v>36.282043642848002</v>
@@ -6411,7 +6444,7 @@
         <v>37458.69</v>
       </c>
       <c r="G226">
-        <v>22.143799999999999</v>
+        <v>21.681000000000001</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.2">
@@ -6419,10 +6452,10 @@
         <v>230</v>
       </c>
       <c r="B227">
-        <v>96.348881804037006</v>
+        <v>96.231437871843994</v>
       </c>
       <c r="C227">
-        <v>91.922729926044994</v>
+        <v>91.918333931239999</v>
       </c>
       <c r="D227">
         <v>37.891239623548003</v>
@@ -6434,7 +6467,7 @@
         <v>36987.86</v>
       </c>
       <c r="G227">
-        <v>21.250800000000002</v>
+        <v>21.270499999999998</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.2">
@@ -6442,10 +6475,10 @@
         <v>231</v>
       </c>
       <c r="B228">
-        <v>99.292310797775997</v>
+        <v>100.03879685202099</v>
       </c>
       <c r="C228">
-        <v>129.942405358695</v>
+        <v>129.92680173917401</v>
       </c>
       <c r="D228">
         <v>37.076740993336998</v>
@@ -6457,7 +6490,7 @@
         <v>41778.870000000003</v>
       </c>
       <c r="G228">
-        <v>20.139800000000001</v>
+        <v>20.381900000000002</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -6465,10 +6498,10 @@
         <v>232</v>
       </c>
       <c r="B229">
-        <v>97.969949138483997</v>
+        <v>97.254765309023995</v>
       </c>
       <c r="C229">
-        <v>126.307615884925</v>
+        <v>126.286116013106</v>
       </c>
       <c r="D229">
         <v>38.748705307191997</v>
@@ -6480,7 +6513,7 @@
         <v>44066.879999999997</v>
       </c>
       <c r="G229">
-        <v>19.9087</v>
+        <v>19.9651</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.2">
@@ -6488,10 +6521,10 @@
         <v>233</v>
       </c>
       <c r="B230">
-        <v>93.104211651510994</v>
+        <v>93.870933699481995</v>
       </c>
       <c r="C230">
-        <v>113.77548817451</v>
+        <v>113.748799524878</v>
       </c>
       <c r="D230">
         <v>39.211395346757001</v>
@@ -6503,7 +6536,7 @@
         <v>42985.73</v>
       </c>
       <c r="G230">
-        <v>20.224799999999998</v>
+        <v>19.921500000000002</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.2">
@@ -6511,10 +6544,10 @@
         <v>234</v>
       </c>
       <c r="B231">
-        <v>90.852149505217994</v>
+        <v>91.172621395872</v>
       </c>
       <c r="C231">
-        <v>89.959220461423996</v>
+        <v>89.941126797403996</v>
       </c>
       <c r="D231">
         <v>38.640136961084998</v>
@@ -6526,7 +6559,7 @@
         <v>44592.91</v>
       </c>
       <c r="G231">
-        <v>20.939</v>
+        <v>20.309699999999999</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.2">
@@ -6534,10 +6567,10 @@
         <v>235</v>
       </c>
       <c r="B232">
-        <v>99.782036513429006</v>
+        <v>98.278066604963001</v>
       </c>
       <c r="C232">
-        <v>83.267552497214993</v>
+        <v>83.252276251656994</v>
       </c>
       <c r="D232">
         <v>40.581572053441</v>
@@ -6549,7 +6582,7 @@
         <v>47246.26</v>
       </c>
       <c r="G232">
-        <v>20.440000000000001</v>
+        <v>20.755500000000001</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.2">
@@ -6557,10 +6590,10 @@
         <v>236</v>
       </c>
       <c r="B233">
-        <v>96.170160175687997</v>
+        <v>96.577826610705003</v>
       </c>
       <c r="C233">
-        <v>94.840263076886004</v>
+        <v>94.819087949215998</v>
       </c>
       <c r="D233">
         <v>42.509073150798997</v>
@@ -6572,7 +6605,7 @@
         <v>48009.72</v>
       </c>
       <c r="G233">
-        <v>20.182200000000002</v>
+        <v>20.0153</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.2">
@@ -6580,10 +6613,10 @@
         <v>237</v>
       </c>
       <c r="B234">
-        <v>98.193630645352002</v>
+        <v>99.285620933599006</v>
       </c>
       <c r="C234">
-        <v>117.304559090598</v>
+        <v>117.27431638128201</v>
       </c>
       <c r="D234">
         <v>42.422701068797998</v>
@@ -6595,7 +6628,7 @@
         <v>50885.95</v>
       </c>
       <c r="G234">
-        <v>19.921299999999999</v>
+        <v>19.963100000000001</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.2">
@@ -6603,10 +6636,10 @@
         <v>238</v>
       </c>
       <c r="B235">
-        <v>98.415385660916002</v>
+        <v>97.826539499158002</v>
       </c>
       <c r="C235">
-        <v>119.13270671610501</v>
+        <v>119.108338830376</v>
       </c>
       <c r="D235">
         <v>44.347676509277001</v>
@@ -6618,7 +6651,7 @@
         <v>50289.75</v>
       </c>
       <c r="G235">
-        <v>19.906199999999998</v>
+        <v>20.030100000000001</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.2">
@@ -6626,10 +6659,10 @@
         <v>245</v>
       </c>
       <c r="B236">
-        <v>97.300227269752</v>
+        <v>97.180219626587004</v>
       </c>
       <c r="C236">
-        <v>108.135491308951</v>
+        <v>108.123475711227</v>
       </c>
       <c r="D236">
         <v>44.293387523756998</v>
@@ -6641,7 +6674,7 @@
         <v>50868.32</v>
       </c>
       <c r="G236">
-        <v>19.845500000000001</v>
+        <v>19.970099999999999</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.2">
@@ -6649,10 +6682,10 @@
         <v>246</v>
       </c>
       <c r="B237">
-        <v>96.063225292469994</v>
+        <v>96.379554025561006</v>
       </c>
       <c r="C237">
-        <v>82.738958673770995</v>
+        <v>82.737723243296003</v>
       </c>
       <c r="D237">
         <v>42.474646633177002</v>
@@ -6664,7 +6697,7 @@
         <v>53304.74</v>
       </c>
       <c r="G237">
-        <v>20.060500000000001</v>
+        <v>20.0761</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.2">
@@ -6672,10 +6705,10 @@
         <v>241</v>
       </c>
       <c r="B238">
-        <v>93.734330162522994</v>
+        <v>93.407891685787007</v>
       </c>
       <c r="C238">
-        <v>78.428870565701999</v>
+        <v>78.431784994514999</v>
       </c>
       <c r="D238">
         <v>43.342082825585997</v>
@@ -6687,7 +6720,7 @@
         <v>51385.55</v>
       </c>
       <c r="G238">
-        <v>20.5623</v>
+        <v>20.0487</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.2">
@@ -6695,10 +6728,10 @@
         <v>242</v>
       </c>
       <c r="B239">
-        <v>96.289783834418003</v>
+        <v>97.047412061206998</v>
       </c>
       <c r="C239">
-        <v>87.948175512277999</v>
+        <v>87.959431478631004</v>
       </c>
       <c r="D239">
         <v>43.843081349925001</v>
@@ -6710,7 +6743,7 @@
         <v>51309.84</v>
       </c>
       <c r="G239">
-        <v>20.529699999999998</v>
+        <v>20.462599999999998</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.2">
@@ -6718,10 +6751,10 @@
         <v>243</v>
       </c>
       <c r="B240">
-        <v>101.126937147889</v>
+        <v>100.618524431319</v>
       </c>
       <c r="C240">
-        <v>136.884318895132</v>
+        <v>136.93932872576499</v>
       </c>
       <c r="D240">
         <v>45.935432245422</v>
@@ -6733,7 +6766,7 @@
         <v>49698.720000000001</v>
       </c>
       <c r="G240">
-        <v>21.4453</v>
+        <v>20.900400000000001</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.2">
@@ -6741,10 +6774,10 @@
         <v>244</v>
       </c>
       <c r="B241">
-        <v>99.703505974840994</v>
+        <v>98.982573996094004</v>
       </c>
       <c r="C241">
-        <v>135.90750412366799</v>
+        <v>135.98741920799301</v>
       </c>
       <c r="D241">
         <v>44.896417492952999</v>
@@ -6756,7 +6789,7 @@
         <v>53272.44</v>
       </c>
       <c r="G241">
-        <v>20.467199999999998</v>
+        <v>20.8918</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.2">
@@ -6764,10 +6797,10 @@
         <v>247</v>
       </c>
       <c r="B242">
-        <v>94.833832335386006</v>
+        <v>95.814116934270999</v>
       </c>
       <c r="C242">
-        <v>111.552370401917</v>
+        <v>111.63584865681401</v>
       </c>
       <c r="D242">
         <v>43.590903532298</v>
@@ -6779,7 +6812,7 @@
         <v>51330.85</v>
       </c>
       <c r="G242">
-        <v>20.635200000000001</v>
+        <v>20.497800000000002</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.2">
@@ -6787,10 +6820,10 @@
         <v>248</v>
       </c>
       <c r="B243">
-        <v>93.688749233989</v>
+        <v>93.914632491301006</v>
       </c>
       <c r="C243">
-        <v>88.120140945596006</v>
+        <v>88.161930135023994</v>
       </c>
       <c r="D243">
         <v>42.940053805837998</v>
@@ -6802,7 +6835,7 @@
         <v>53400.61</v>
       </c>
       <c r="G243">
-        <v>20.425699999999999</v>
+        <v>20.4495</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.2">
@@ -6810,10 +6843,10 @@
         <v>249</v>
       </c>
       <c r="B244">
-        <v>101.662125835108</v>
+        <v>99.967807647239994</v>
       </c>
       <c r="C244">
-        <v>88.023945634984003</v>
+        <v>88.046026185125996</v>
       </c>
       <c r="D244">
         <v>43.560277939671998</v>
@@ -6825,7 +6858,7 @@
         <v>56536.68</v>
       </c>
       <c r="G244">
-        <v>19.911200000000001</v>
+        <v>20.5562</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.2">
@@ -6833,10 +6866,10 @@
         <v>250</v>
       </c>
       <c r="B245">
-        <v>98.590944247983998</v>
+        <v>99.349741652252007</v>
       </c>
       <c r="C245">
-        <v>97.166377064014995</v>
+        <v>97.163813384075993</v>
       </c>
       <c r="D245">
         <v>44.301709560652</v>
@@ -6848,7 +6881,7 @@
         <v>51417.97</v>
       </c>
       <c r="G245">
-        <v>20.372800000000002</v>
+        <v>20.108799999999999</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.2">
@@ -6856,10 +6889,10 @@
         <v>251</v>
       </c>
       <c r="B246">
-        <v>101.68171628160999</v>
+        <v>101.95598526481599</v>
       </c>
       <c r="C246">
-        <v>121.392875379481</v>
+        <v>121.328212991111</v>
       </c>
       <c r="D246">
         <v>43.782312077302997</v>
@@ -6871,7 +6904,7 @@
         <v>51752.53</v>
       </c>
       <c r="G246">
-        <v>19.693999999999999</v>
+        <v>20.0305</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.2">
@@ -6879,10 +6912,10 @@
         <v>252</v>
       </c>
       <c r="B247">
-        <v>100.261327972152</v>
+        <v>99.908891189290003</v>
       </c>
       <c r="C247">
-        <v>111.11032805113</v>
+        <v>110.947699708503</v>
       </c>
       <c r="D247">
         <v>43.208627089887997</v>
@@ -6894,7 +6927,7 @@
         <v>47524.45</v>
       </c>
       <c r="G247">
-        <v>20.133500000000002</v>
+        <v>20.023700000000002</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.2">
@@ -6902,10 +6935,10 @@
         <v>239</v>
       </c>
       <c r="B248">
-        <v>99.736088676582</v>
+        <v>100.508170619061</v>
       </c>
       <c r="C248">
-        <v>102.448256467674</v>
+        <v>102.190307584381</v>
       </c>
       <c r="D248">
         <v>41.269872650913001</v>
@@ -6917,7 +6950,7 @@
         <v>48144.33</v>
       </c>
       <c r="G248">
-        <v>20.348500000000001</v>
+        <v>20.546700000000001</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.2">
@@ -6925,10 +6958,10 @@
         <v>240</v>
       </c>
       <c r="B249">
-        <v>101.65688943813301</v>
+        <v>101.01171329554001</v>
       </c>
       <c r="C249">
-        <v>85.264453594436006</v>
+        <v>84.975120397590999</v>
       </c>
       <c r="D249">
         <v>40.297933839210003</v>
@@ -6940,7 +6973,7 @@
         <v>44919.22</v>
       </c>
       <c r="G249">
-        <v>20.0962</v>
+        <v>20.120899999999999</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.2">
@@ -6948,10 +6981,10 @@
         <v>253</v>
       </c>
       <c r="B250">
-        <v>98.765332430360999</v>
+        <v>98.379287082857005</v>
       </c>
       <c r="C250">
-        <v>84.036521416339994</v>
+        <v>83.656480165770006</v>
       </c>
       <c r="D250">
         <v>40.822792165000003</v>
@@ -6963,7 +6996,7 @@
         <v>44626.8</v>
       </c>
       <c r="G250">
-        <v>20.092500000000001</v>
+        <v>20.074999999999999</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.2">
@@ -6971,10 +7004,10 @@
         <v>254</v>
       </c>
       <c r="B251">
-        <v>100.627900593531</v>
+        <v>101.882677944161</v>
       </c>
       <c r="C251">
-        <v>91.089466365006999</v>
+        <v>91.164301495331003</v>
       </c>
       <c r="D251">
         <v>41.283880015538998</v>
@@ -6986,7 +7019,7 @@
         <v>49922.3</v>
       </c>
       <c r="G251">
-        <v>19.8245</v>
+        <v>19.984500000000001</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.2">
@@ -6994,10 +7027,10 @@
         <v>255</v>
       </c>
       <c r="B252">
-        <v>105.62896593180901</v>
+        <v>105.19530989596799</v>
       </c>
       <c r="C252">
-        <v>144.49196388394299</v>
+        <v>145.43754722297601</v>
       </c>
       <c r="D252">
         <v>41.755955250832002</v>
@@ -7009,7 +7042,7 @@
         <v>51684.86</v>
       </c>
       <c r="G252">
-        <v>19.3965</v>
+        <v>19.444900000000001</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -7017,10 +7050,10 @@
         <v>256</v>
       </c>
       <c r="B253">
-        <v>103.72796240074599</v>
+        <v>103.85864446234</v>
       </c>
       <c r="C253">
-        <v>142.65191182067099</v>
+        <v>142.64132309848901</v>
       </c>
       <c r="D253">
         <v>43.287305150133001</v>
@@ -7032,7 +7065,7 @@
         <v>48463.86</v>
       </c>
       <c r="G253">
-        <v>19.471499999999999</v>
+        <v>19.593</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.2">
@@ -7040,10 +7073,10 @@
         <v>257</v>
       </c>
       <c r="B254">
-        <v>99.273658429909005</v>
+        <v>99.709560373724003</v>
       </c>
       <c r="C254">
-        <v>107.489863893953</v>
+        <v>108.608164862796</v>
       </c>
       <c r="D254">
         <v>44.774005908794003</v>
@@ -7055,7 +7088,7 @@
         <v>54564.27</v>
       </c>
       <c r="G254">
-        <v>18.793700000000001</v>
+        <v>18.9863</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.2">
@@ -7063,10 +7096,10 @@
         <v>258</v>
       </c>
       <c r="B255">
-        <v>96.759142591471004</v>
+        <v>97.491386810804997</v>
       </c>
       <c r="C255">
-        <v>94.238780553219996</v>
+        <v>96.180035583050994</v>
       </c>
       <c r="D255">
         <v>44.648579360698001</v>
@@ -7078,7 +7111,7 @@
         <v>52758.06</v>
       </c>
       <c r="G255">
-        <v>18.344799999999999</v>
+        <v>18.598600000000001</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.2">
@@ -7086,10 +7119,10 @@
         <v>259</v>
       </c>
       <c r="B256">
-        <v>104.092569211742</v>
+        <v>102.62144393337201</v>
       </c>
       <c r="C256">
-        <v>85.691416385902002</v>
+        <v>86.716938029353997</v>
       </c>
       <c r="D256">
         <v>44.497504601820999</v>
@@ -7101,7 +7134,7 @@
         <v>53904</v>
       </c>
       <c r="G256">
-        <v>18.041499999999999</v>
+        <v>18.3749</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
@@ -7109,10 +7142,10 @@
         <v>260</v>
       </c>
       <c r="B257">
-        <v>100.438899133793</v>
+        <v>102.460969476016</v>
       </c>
       <c r="C257">
-        <v>97.724003145099999</v>
+        <v>99.051072436629994</v>
       </c>
       <c r="D257">
         <v>44.604057252018997</v>
@@ -7124,7 +7157,7 @@
         <v>55121.22</v>
       </c>
       <c r="G257">
-        <v>17.997499999999999</v>
+        <v>18.0855</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -7132,10 +7165,10 @@
         <v>261</v>
       </c>
       <c r="B258">
-        <v>106.186349288073</v>
+        <v>105.369408531378</v>
       </c>
       <c r="C258">
-        <v>117.83166281374299</v>
+        <v>118.655938302796</v>
       </c>
       <c r="D258">
         <v>44.672420334263002</v>
@@ -7147,18 +7180,18 @@
         <v>52736.26</v>
       </c>
       <c r="G258">
-        <v>17.741800000000001</v>
+        <v>17.737300000000001</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B259">
-        <v>104.442413495718</v>
+        <v>103.83634325123199</v>
       </c>
       <c r="C259">
-        <v>113.29002897126099</v>
+        <v>113.096416328779</v>
       </c>
       <c r="D259">
         <v>45.900081964233003</v>
@@ -7170,18 +7203,18 @@
         <v>53526.1</v>
       </c>
       <c r="G259">
-        <v>17.1358</v>
+        <v>17.241199999999999</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B260">
-        <v>102.84110671657101</v>
+        <v>104.188589598927</v>
       </c>
       <c r="C260">
-        <v>102.096662761518</v>
+        <v>102.58863626795799</v>
       </c>
       <c r="D260">
         <v>46.382665573225999</v>
@@ -7193,18 +7226,18 @@
         <v>54819.05</v>
       </c>
       <c r="G260">
-        <v>16.7303</v>
+        <v>16.904900000000001</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B261">
-        <v>105.38761306281999</v>
+        <v>104.598699099454</v>
       </c>
       <c r="C261">
-        <v>86.555920767535994</v>
+        <v>86.985835689602993</v>
       </c>
       <c r="D261">
         <v>46.082397318317</v>
@@ -7216,18 +7249,18 @@
         <v>53020.98</v>
       </c>
       <c r="G261">
-        <v>16.917000000000002</v>
+        <v>16.976600000000001</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B262">
-        <v>102.319528889284</v>
+        <v>102.991980596546</v>
       </c>
       <c r="C262">
-        <v>82.838144411884997</v>
+        <v>82.963037234606006</v>
       </c>
       <c r="D262">
         <v>46.378813796553999</v>
@@ -7239,18 +7272,18 @@
         <v>50874.98</v>
       </c>
       <c r="G262">
-        <v>17.412700000000001</v>
+        <v>17.307700000000001</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B263">
-        <v>104.866061984346</v>
+        <v>106.067574904699</v>
       </c>
       <c r="C263">
-        <v>92.598614142334995</v>
+        <v>93.218263426215003</v>
       </c>
       <c r="D263">
         <v>45.669149771775999</v>
@@ -7262,18 +7295,18 @@
         <v>49061.88</v>
       </c>
       <c r="G263">
-        <v>18.036799999999999</v>
+        <v>18.0823</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B264">
-        <v>107.81850771828201</v>
+        <v>107.751350961339</v>
       </c>
       <c r="C264">
-        <v>126.455777995332</v>
+        <v>125.476339485244</v>
       </c>
       <c r="D264">
         <v>46.899020937591999</v>
@@ -7285,18 +7318,18 @@
         <v>54060.01</v>
       </c>
       <c r="G264">
-        <v>17.373000000000001</v>
+        <v>17.3767</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B265">
-        <v>104.751210871084</v>
+        <v>105.773402762282</v>
       </c>
       <c r="C265">
-        <v>140.66685978418701</v>
+        <v>137.98538809570101</v>
       </c>
       <c r="D265">
         <v>47.185889143993997</v>
@@ -7308,18 +7341,18 @@
         <v>57386.25</v>
       </c>
       <c r="G265">
-        <v>16.919</v>
+        <v>17.186</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B266">
-        <v>101.133499468585</v>
+        <v>100.615378579539</v>
       </c>
       <c r="C266">
-        <v>95.392172101518995</v>
+        <v>93.112961115499999</v>
       </c>
       <c r="D266">
         <v>47.571614440638001</v>
@@ -7331,18 +7364,18 @@
         <v>57372.76</v>
       </c>
       <c r="G266">
-        <v>17.1633</v>
+        <v>17.087299999999999</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B267">
-        <v>100.94522633813</v>
+        <v>100.087079117264</v>
       </c>
       <c r="C267">
-        <v>98.561588825596004</v>
+        <v>97.205858357883002</v>
       </c>
       <c r="D267">
         <v>47.125446530714001</v>
@@ -7354,18 +7387,18 @@
         <v>55414</v>
       </c>
       <c r="G267">
-        <v>17.063300000000002</v>
+        <v>17.0898</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B268">
-        <v>102.69601303330499</v>
+        <v>105.981413261917</v>
       </c>
       <c r="C268">
-        <v>86.293998990435</v>
+        <v>86.488927669240994</v>
       </c>
       <c r="D268">
         <v>47.37701218166</v>
@@ -7377,18 +7410,18 @@
         <v>57369.01</v>
       </c>
       <c r="G268">
-        <v>16.532299999999999</v>
+        <v>16.791799999999999</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B269">
-        <v>105.761269866756</v>
+        <v>103.252023853586</v>
       </c>
       <c r="C269">
-        <v>93.616457865835997</v>
+        <v>94.584079325798001</v>
       </c>
       <c r="D269">
         <v>47.734665663569999</v>
@@ -7400,18 +7433,18 @@
         <v>56727.98</v>
       </c>
       <c r="G269">
-        <v>17.095800000000001</v>
+        <v>16.810400000000001</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B270">
-        <v>107.86808110183399</v>
+        <v>107.151082234957</v>
       </c>
       <c r="C270">
-        <v>115.73739715082399</v>
+        <v>113.820274798376</v>
       </c>
       <c r="D270">
         <v>46.695694705173999</v>
@@ -7423,18 +7456,18 @@
         <v>55179.24</v>
       </c>
       <c r="G270">
-        <v>17.017700000000001</v>
+        <v>16.793600000000001</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B271">
-        <v>103.81562240224901</v>
+        <v>105.124313429908</v>
       </c>
       <c r="C271">
-        <v>109.980170028453</v>
+        <v>106.762964423887</v>
       </c>
       <c r="D271">
         <v>48.053007238749998</v>
@@ -7446,7 +7479,260 @@
         <v>52440.02</v>
       </c>
       <c r="G271">
-        <v>18.247800000000002</v>
+        <v>18.217400000000001</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>275</v>
+      </c>
+      <c r="B272">
+        <v>106.34087557962199</v>
+      </c>
+      <c r="C272">
+        <v>113.83395003286699</v>
+      </c>
+      <c r="D272">
+        <v>46.966746692724001</v>
+      </c>
+      <c r="E272">
+        <v>52.082464717969003</v>
+      </c>
+      <c r="F272">
+        <v>53093.97</v>
+      </c>
+      <c r="G272">
+        <v>18.111699999999999</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>276</v>
+      </c>
+      <c r="B273">
+        <v>105.953954063867</v>
+      </c>
+      <c r="C273">
+        <v>83.686744864334997</v>
+      </c>
+      <c r="D273">
+        <v>46.993258614231998</v>
+      </c>
+      <c r="E273">
+        <v>51.510702911511999</v>
+      </c>
+      <c r="F273">
+        <v>51985.87</v>
+      </c>
+      <c r="G273">
+        <v>19.151499999999999</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>277</v>
+      </c>
+      <c r="B274">
+        <v>103.974825485175</v>
+      </c>
+      <c r="C274">
+        <v>81.920398626354995</v>
+      </c>
+      <c r="D274">
+        <v>46.565337126157999</v>
+      </c>
+      <c r="E274">
+        <v>51.441561516001997</v>
+      </c>
+      <c r="F274">
+        <v>52477.3</v>
+      </c>
+      <c r="G274">
+        <v>19.631599999999999</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>278</v>
+      </c>
+      <c r="B275">
+        <v>105.660735747077</v>
+      </c>
+      <c r="C275">
+        <v>86.945461369037005</v>
+      </c>
+      <c r="D275">
+        <v>48.897877633122</v>
+      </c>
+      <c r="E275">
+        <v>51.982855855876998</v>
+      </c>
+      <c r="F275">
+        <v>50661.05</v>
+      </c>
+      <c r="G275">
+        <v>19.706199999999999</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>279</v>
+      </c>
+      <c r="B276">
+        <v>108.533356180228</v>
+      </c>
+      <c r="C276">
+        <v>122.37686014653001</v>
+      </c>
+      <c r="D276">
+        <v>47.442950378912002</v>
+      </c>
+      <c r="E276">
+        <v>51.705833883170001</v>
+      </c>
+      <c r="F276">
+        <v>49812.639999999999</v>
+      </c>
+      <c r="G276">
+        <v>20.345500000000001</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>280</v>
+      </c>
+      <c r="B277">
+        <v>104.68701186309799</v>
+      </c>
+      <c r="C277">
+        <v>126.842545329866</v>
+      </c>
+      <c r="D277">
+        <v>47.270034347409002</v>
+      </c>
+      <c r="E277">
+        <v>51.594970537645999</v>
+      </c>
+      <c r="F277">
+        <v>49513.27</v>
+      </c>
+      <c r="G277">
+        <v>20.266100000000002</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>281</v>
+      </c>
+      <c r="B278">
+        <v>100.580717205765</v>
+      </c>
+      <c r="C278">
+        <v>106.871526629904</v>
+      </c>
+      <c r="D278">
+        <v>47.149656125926001</v>
+      </c>
+      <c r="E278">
+        <v>52.093663787578997</v>
+      </c>
+      <c r="F278">
+        <v>51209.53</v>
+      </c>
+      <c r="G278">
+        <v>20.548999999999999</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>282</v>
+      </c>
+      <c r="B279">
+        <v>100.899587210063</v>
+      </c>
+      <c r="C279">
+        <v>96.091712524789997</v>
+      </c>
+      <c r="D279">
+        <v>46.488366486733</v>
+      </c>
+      <c r="E279">
+        <v>51.554709731732999</v>
+      </c>
+      <c r="F279">
+        <v>52325.73</v>
+      </c>
+      <c r="G279">
+        <v>20.457100000000001</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>283</v>
+      </c>
+      <c r="B280">
+        <v>105.80887852017101</v>
+      </c>
+      <c r="C280">
+        <v>94.762388364112994</v>
+      </c>
+      <c r="D280">
+        <v>46.090078149416001</v>
+      </c>
+      <c r="E280">
+        <v>51.713886002711</v>
+      </c>
+      <c r="F280">
+        <v>52484.43</v>
+      </c>
+      <c r="G280">
+        <v>20.241700000000002</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>284</v>
+      </c>
+      <c r="B281">
+        <v>104.33151888376101</v>
+      </c>
+      <c r="C281">
+        <v>93.172301484505994</v>
+      </c>
+      <c r="D281">
+        <v>45.454235606749997</v>
+      </c>
+      <c r="E281">
+        <v>51.322182008265003</v>
+      </c>
+      <c r="F281">
+        <v>56259.28</v>
+      </c>
+      <c r="G281">
+        <v>20.0564</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>285</v>
+      </c>
+      <c r="B282">
+        <v>107.532926647286</v>
+      </c>
+      <c r="C282">
+        <v>120.02319362474999</v>
+      </c>
+      <c r="D282">
+        <v>46.497801253238002</v>
+      </c>
+      <c r="E282">
+        <v>52.174658656033003</v>
+      </c>
+      <c r="F282">
+        <v>57841.69</v>
+      </c>
+      <c r="G282">
+        <v>19.435500000000001</v>
       </c>
     </row>
   </sheetData>
